--- a/news_daily/2026-08-30.xlsx
+++ b/news_daily/2026-08-30.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BH$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BH$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BH$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BH$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -43,7 +43,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -53,11 +53,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFCDD2"/>
       </patternFill>
     </fill>
     <fill>
@@ -89,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -101,9 +96,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -471,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH12"/>
+  <dimension ref="A1:BL12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -534,6 +526,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -835,6 +831,26 @@
       <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Ticker稽核警示</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
         </is>
       </c>
     </row>
@@ -1007,6 +1023,10 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1038,12 +1058,12 @@
       <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>違約</t>
+          <t>重大訴訟</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -1053,17 +1073,17 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -1099,7 +1119,7 @@
       </c>
       <c r="Y3" s="3" t="inlineStr">
         <is>
-          <t>DEFAULT</t>
+          <t>MAJOR_LITIGATION</t>
         </is>
       </c>
       <c r="Z3" s="3" t="inlineStr">
@@ -1108,7 +1128,11 @@
         </is>
       </c>
       <c r="AA3" s="3" t="inlineStr"/>
-      <c r="AB3" s="3" t="inlineStr"/>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>c90316d5cd9f4f858e19e3d703fc4cb5</t>
+        </is>
+      </c>
       <c r="AC3" s="3" t="inlineStr">
         <is>
           <t>7210521af56fdba6a7b60a22</t>
@@ -1131,7 +1155,7 @@
       <c r="AN3" s="3" t="inlineStr"/>
       <c r="AO3" s="3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP3" s="3" t="inlineStr"/>
@@ -1173,6 +1197,22 @@
       </c>
       <c r="BG3" s="3" t="inlineStr"/>
       <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BI3" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:43:17.016263+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1343,346 +1383,402 @@
         </is>
       </c>
       <c r="BH4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr"/>
+      <c r="BJ4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr"/>
+      <c r="BL4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>EFX</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Equifax, Inc. Common Stock</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>2026-08-30T15:37:01+08:00</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Did Equifax's (EFX) Dividend Steadiness and Legal Settlement Proposal Just Reframe Its Risk‑Reward Profile?</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>監管裁罰</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>0.204</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr"/>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQNGpnZ2lNck9WMTA5VG4wajJoU05HdFdqTHhGYkZ0QXdybnBPZEFMcVdmTDBKbHV3VVRiRGtKRkRHZWM4SDNubGFLelc4S2laQXV0WHZscmNrSVgxLWlMUGFOQmtGRDZsTDZwbFVkUU1KelRiWTc2czJmYTBmS250MWVITGpzalVObVdsMkd6dmZfTVRoemtWTXZ5alJkcDIzY0FEdU9GUU1CXzI0NTd4YlRFSkpFWThSRXdjQ2hIRlkzVkVjUUdzNUNOYjZ0enPSAdQBQVVfeXFMTkwyS2FESkhtLWFCTktzTmsyVXN4akc4djVTVG51STVlMHctVUNVUm5LTG90NXpLbTZkVnU4T3F3UnNiZ0R5RjkweUkzcl9ZZDc1bVBWMlhyVjhsTEtNanhUNENTSl9mUUN2SFpCMWlmRVZidVFPN1gzQXNZelpCSS1iVURNLS1YczBLT0psNEZib0FoVGViV0JwMGt4dXZld2RCZFRNNEFMMkZINElxYmZ4MllyWUw1bHRsYmlOaktwZTA2OV9YX3JwNjA3NHdPLU1sY1Y?oc=5</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>simplywall.st</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>8f0aec19b8c84a968ee34a0f1df44b85</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>4df3441d339fa556fbe78fd4</t>
+        </is>
+      </c>
+      <c r="AD5" s="2" t="inlineStr">
+        <is>
+          <t>9171d3d5d6a05bdc43f8277c</t>
+        </is>
+      </c>
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
+      <c r="AG5" s="2" t="inlineStr"/>
+      <c r="AH5" s="2" t="inlineStr"/>
+      <c r="AI5" s="2" t="inlineStr"/>
+      <c r="AJ5" s="2" t="inlineStr"/>
+      <c r="AK5" s="2" t="inlineStr"/>
+      <c r="AL5" s="2" t="inlineStr"/>
+      <c r="AM5" s="2" t="inlineStr"/>
+      <c r="AN5" s="2" t="inlineStr"/>
+      <c r="AO5" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O5" s="4" t="inlineStr">
-        <is>
-          <t>0.204</t>
-        </is>
-      </c>
-      <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr"/>
-      <c r="R5" s="4" t="inlineStr"/>
-      <c r="S5" s="4" t="inlineStr"/>
-      <c r="T5" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U5" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQNGpnZ2lNck9WMTA5VG4wajJoU05HdFdqTHhGYkZ0QXdybnBPZEFMcVdmTDBKbHV3VVRiRGtKRkRHZWM4SDNubGFLelc4S2laQXV0WHZscmNrSVgxLWlMUGFOQmtGRDZsTDZwbFVkUU1KelRiWTc2czJmYTBmS250MWVITGpzalVObVdsMkd6dmZfTVRoemtWTXZ5alJkcDIzY0FEdU9GUU1CXzI0NTd4YlRFSkpFWThSRXdjQ2hIRlkzVkVjUUdzNUNOYjZ0enPSAdQBQVVfeXFMTkwyS2FESkhtLWFCTktzTmsyVXN4akc4djVTVG51STVlMHctVUNVUm5LTG90NXpLbTZkVnU4T3F3UnNiZ0R5RjkweUkzcl9ZZDc1bVBWMlhyVjhsTEtNanhUNENTSl9mUUN2SFpCMWlmRVZidVFPN1gzQXNZelpCSS1iVURNLS1YczBLT0psNEZib0FoVGViV0JwMGt4dXZld2RCZFRNNEFMMkZINElxYmZ4MllyWUw1bHRsYmlOaktwZTA2OV9YX3JwNjA3NHdPLU1sY1Y?oc=5</t>
-        </is>
-      </c>
-      <c r="V5" s="4" t="inlineStr">
-        <is>
-          <t>simplywall.st</t>
-        </is>
-      </c>
-      <c r="W5" s="4" t="inlineStr"/>
-      <c r="X5" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y5" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z5" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA5" s="4" t="inlineStr"/>
-      <c r="AB5" s="4" t="inlineStr"/>
-      <c r="AC5" s="4" t="inlineStr">
-        <is>
-          <t>4df3441d339fa556fbe78fd4</t>
-        </is>
-      </c>
-      <c r="AD5" s="4" t="inlineStr">
-        <is>
-          <t>9171d3d5d6a05bdc43f8277c</t>
-        </is>
-      </c>
-      <c r="AE5" s="4" t="inlineStr"/>
-      <c r="AF5" s="4" t="inlineStr"/>
-      <c r="AG5" s="4" t="inlineStr"/>
-      <c r="AH5" s="4" t="inlineStr"/>
-      <c r="AI5" s="4" t="inlineStr"/>
-      <c r="AJ5" s="4" t="inlineStr"/>
-      <c r="AK5" s="4" t="inlineStr"/>
-      <c r="AL5" s="4" t="inlineStr"/>
-      <c r="AM5" s="4" t="inlineStr"/>
-      <c r="AN5" s="4" t="inlineStr"/>
-      <c r="AO5" s="4" t="inlineStr"/>
-      <c r="AP5" s="4" t="inlineStr"/>
-      <c r="AQ5" s="4" t="inlineStr"/>
-      <c r="AR5" s="4" t="inlineStr"/>
-      <c r="AS5" s="4" t="inlineStr"/>
-      <c r="AT5" s="4" t="inlineStr"/>
-      <c r="AU5" s="4" t="inlineStr"/>
-      <c r="AV5" s="4" t="inlineStr"/>
-      <c r="AW5" s="4" t="inlineStr">
+      <c r="AP5" s="2" t="inlineStr"/>
+      <c r="AQ5" s="2" t="inlineStr"/>
+      <c r="AR5" s="2" t="inlineStr"/>
+      <c r="AS5" s="2" t="inlineStr"/>
+      <c r="AT5" s="2" t="inlineStr"/>
+      <c r="AU5" s="2" t="inlineStr"/>
+      <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" s="2" t="inlineStr">
         <is>
           <t>NYSE</t>
         </is>
       </c>
-      <c r="AX5" s="4" t="inlineStr"/>
-      <c r="AY5" s="4" t="inlineStr"/>
-      <c r="AZ5" s="4" t="inlineStr"/>
-      <c r="BA5" s="4" t="inlineStr"/>
-      <c r="BB5" s="4" t="inlineStr">
+      <c r="AX5" s="2" t="inlineStr"/>
+      <c r="AY5" s="2" t="inlineStr"/>
+      <c r="AZ5" s="2" t="inlineStr"/>
+      <c r="BA5" s="2" t="inlineStr"/>
+      <c r="BB5" s="2" t="inlineStr">
         <is>
           <t>EFX</t>
         </is>
       </c>
-      <c r="BC5" s="4" t="inlineStr">
+      <c r="BC5" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD5" s="4" t="inlineStr"/>
-      <c r="BE5" s="4" t="inlineStr">
+      <c r="BD5" s="2" t="inlineStr"/>
+      <c r="BE5" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF5" s="4" t="inlineStr">
+      <c r="BF5" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG5" s="4" t="inlineStr">
+      <c r="BG5" s="2" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH5" s="4" t="inlineStr"/>
+      <c r="BH5" s="2" t="inlineStr"/>
+      <c r="BI5" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ5" s="2" t="inlineStr"/>
+      <c r="BK5" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>META</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Meta Platforms, Inc.</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>2026-08-30T15:00:00+08:00</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>This week's Meta settlement will reverberate across the world for years</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>監管裁罰</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>0.099</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr"/>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE5wWHRSVFl5ZHFlR1NwYmJwNDNld1l1d3ZLS19wZU9aYjFlY1RYZWpBWFN0c3Q4YmN3dHlUWlRSY25nMFR6S3Azb1A2ci1tbjE3VkVZV2FqNHpmc1hnQkVhQldwcmk?oc=5</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>Tech Policy Press</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr"/>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr"/>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>ac8a9ef184c544b788e8cf2469746289</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>ed2de18d801507fb35a62f33</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr">
+        <is>
+          <t>edbb4144ee531b884bbb6c3d</t>
+        </is>
+      </c>
+      <c r="AE6" s="3" t="inlineStr"/>
+      <c r="AF6" s="3" t="inlineStr"/>
+      <c r="AG6" s="3" t="inlineStr"/>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr"/>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr"/>
+      <c r="AM6" s="3" t="inlineStr"/>
+      <c r="AN6" s="3" t="inlineStr"/>
+      <c r="AO6" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O6" s="4" t="inlineStr">
-        <is>
-          <t>0.099</t>
-        </is>
-      </c>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U6" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE5wWHRSVFl5ZHFlR1NwYmJwNDNld1l1d3ZLS19wZU9aYjFlY1RYZWpBWFN0c3Q4YmN3dHlUWlRSY25nMFR6S3Azb1A2ci1tbjE3VkVZV2FqNHpmc1hnQkVhQldwcmk?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="4" t="inlineStr">
-        <is>
-          <t>Tech Policy Press</t>
-        </is>
-      </c>
-      <c r="W6" s="4" t="inlineStr"/>
-      <c r="X6" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y6" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z6" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA6" s="4" t="inlineStr"/>
-      <c r="AB6" s="4" t="inlineStr"/>
-      <c r="AC6" s="4" t="inlineStr">
-        <is>
-          <t>ed2de18d801507fb35a62f33</t>
-        </is>
-      </c>
-      <c r="AD6" s="4" t="inlineStr">
-        <is>
-          <t>edbb4144ee531b884bbb6c3d</t>
-        </is>
-      </c>
-      <c r="AE6" s="4" t="inlineStr"/>
-      <c r="AF6" s="4" t="inlineStr"/>
-      <c r="AG6" s="4" t="inlineStr"/>
-      <c r="AH6" s="4" t="inlineStr"/>
-      <c r="AI6" s="4" t="inlineStr"/>
-      <c r="AJ6" s="4" t="inlineStr"/>
-      <c r="AK6" s="4" t="inlineStr"/>
-      <c r="AL6" s="4" t="inlineStr"/>
-      <c r="AM6" s="4" t="inlineStr"/>
-      <c r="AN6" s="4" t="inlineStr"/>
-      <c r="AO6" s="4" t="inlineStr"/>
-      <c r="AP6" s="4" t="inlineStr"/>
-      <c r="AQ6" s="4" t="inlineStr"/>
-      <c r="AR6" s="4" t="inlineStr"/>
-      <c r="AS6" s="4" t="inlineStr"/>
-      <c r="AT6" s="4" t="inlineStr"/>
-      <c r="AU6" s="4" t="inlineStr"/>
-      <c r="AV6" s="4" t="inlineStr"/>
-      <c r="AW6" s="4" t="inlineStr">
+      <c r="AP6" s="3" t="inlineStr"/>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr"/>
+      <c r="AS6" s="3" t="inlineStr"/>
+      <c r="AT6" s="3" t="inlineStr"/>
+      <c r="AU6" s="3" t="inlineStr"/>
+      <c r="AV6" s="3" t="inlineStr"/>
+      <c r="AW6" s="3" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX6" s="4" t="inlineStr"/>
-      <c r="AY6" s="4" t="inlineStr"/>
-      <c r="AZ6" s="4" t="inlineStr"/>
-      <c r="BA6" s="4" t="inlineStr"/>
-      <c r="BB6" s="4" t="inlineStr">
+      <c r="AX6" s="3" t="inlineStr"/>
+      <c r="AY6" s="3" t="inlineStr"/>
+      <c r="AZ6" s="3" t="inlineStr"/>
+      <c r="BA6" s="3" t="inlineStr"/>
+      <c r="BB6" s="3" t="inlineStr">
         <is>
           <t>META</t>
         </is>
       </c>
-      <c r="BC6" s="4" t="inlineStr">
+      <c r="BC6" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD6" s="4" t="inlineStr"/>
-      <c r="BE6" s="4" t="inlineStr">
+      <c r="BD6" s="3" t="inlineStr"/>
+      <c r="BE6" s="3" t="inlineStr">
         <is>
           <t>https://investor.atmeta.com/stock-info/default.aspx</t>
         </is>
       </c>
-      <c r="BF6" s="4" t="inlineStr">
+      <c r="BF6" s="3" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="BG6" s="4" t="inlineStr">
+      <c r="BG6" s="3" t="inlineStr">
         <is>
           <t>上市公司</t>
         </is>
       </c>
-      <c r="BH6" s="4" t="inlineStr"/>
+      <c r="BH6" s="3" t="inlineStr"/>
+      <c r="BI6" s="3" t="inlineStr"/>
+      <c r="BJ6" s="3" t="inlineStr"/>
+      <c r="BK6" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1853,6 +1949,10 @@
       </c>
       <c r="BG7" s="2" t="inlineStr"/>
       <c r="BH7" s="2" t="inlineStr"/>
+      <c r="BI7" s="2" t="inlineStr"/>
+      <c r="BJ7" s="2" t="inlineStr"/>
+      <c r="BK7" s="2" t="inlineStr"/>
+      <c r="BL7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2023,6 +2123,10 @@
         </is>
       </c>
       <c r="BH8" s="2" t="inlineStr"/>
+      <c r="BI8" s="2" t="inlineStr"/>
+      <c r="BJ8" s="2" t="inlineStr"/>
+      <c r="BK8" s="2" t="inlineStr"/>
+      <c r="BL8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2193,511 +2297,567 @@
         </is>
       </c>
       <c r="BH9" s="2" t="inlineStr"/>
+      <c r="BI9" s="2" t="inlineStr"/>
+      <c r="BJ9" s="2" t="inlineStr"/>
+      <c r="BK9" s="2" t="inlineStr"/>
+      <c r="BL9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>WMT</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Walmart Inc.</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>2026-08-30T05:24:49+08:00</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>Walmart agrees to pay $50M settlement over allegations its pharmacies filled illegal opioid prescriptions</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr"/>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>監管裁罰</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L10" s="4" t="inlineStr"/>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>'-0.678</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr"/>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxNUDNOU2xVQXUtM3NYR0t2VFZ1ckV1QjBlYzBnVFVYYmZPeE91bUlvT0FKZ1haUkZzUVFPMExfWVpPS2syUWxPenJ6bGczRUd2UHFMRHh3R2pRa2VoRjZyNG91RUc0dmF1amU4NFB0ZW5TcFFhMDU4T1RaX3lOVE5oRHJ1enNVOXJiSk5LNkprWUZleXpydDhjRVRxRk14Nl9HRXZUajBPTlphT2tpcnk5WWNFdklRQnJpWGE0NTJMb1JfVkF1QWRLYjF6SFgyZw?oc=5</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>FOX 7 Austin</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr"/>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr"/>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>7a2d3908ea6049d993fd4df901a2530b</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>5f8fefd1073085060d66d2a3</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr">
+        <is>
+          <t>66ab313c9e99b9661237f750</t>
+        </is>
+      </c>
+      <c r="AE10" s="3" t="inlineStr"/>
+      <c r="AF10" s="3" t="inlineStr"/>
+      <c r="AG10" s="3" t="inlineStr"/>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr"/>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr"/>
+      <c r="AM10" s="3" t="inlineStr"/>
+      <c r="AN10" s="3" t="inlineStr"/>
+      <c r="AO10" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O10" s="4" t="inlineStr">
-        <is>
-          <t>'-0.678</t>
-        </is>
-      </c>
-      <c r="P10" s="4" t="inlineStr"/>
-      <c r="Q10" s="4" t="inlineStr"/>
-      <c r="R10" s="4" t="inlineStr"/>
-      <c r="S10" s="4" t="inlineStr"/>
-      <c r="T10" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U10" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxNUDNOU2xVQXUtM3NYR0t2VFZ1ckV1QjBlYzBnVFVYYmZPeE91bUlvT0FKZ1haUkZzUVFPMExfWVpPS2syUWxPenJ6bGczRUd2UHFMRHh3R2pRa2VoRjZyNG91RUc0dmF1amU4NFB0ZW5TcFFhMDU4T1RaX3lOVE5oRHJ1enNVOXJiSk5LNkprWUZleXpydDhjRVRxRk14Nl9HRXZUajBPTlphT2tpcnk5WWNFdklRQnJpWGE0NTJMb1JfVkF1QWRLYjF6SFgyZw?oc=5</t>
-        </is>
-      </c>
-      <c r="V10" s="4" t="inlineStr">
-        <is>
-          <t>FOX 7 Austin</t>
-        </is>
-      </c>
-      <c r="W10" s="4" t="inlineStr"/>
-      <c r="X10" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y10" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z10" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA10" s="4" t="inlineStr"/>
-      <c r="AB10" s="4" t="inlineStr"/>
-      <c r="AC10" s="4" t="inlineStr">
-        <is>
-          <t>5f8fefd1073085060d66d2a3</t>
-        </is>
-      </c>
-      <c r="AD10" s="4" t="inlineStr">
-        <is>
-          <t>66ab313c9e99b9661237f750</t>
-        </is>
-      </c>
-      <c r="AE10" s="4" t="inlineStr"/>
-      <c r="AF10" s="4" t="inlineStr"/>
-      <c r="AG10" s="4" t="inlineStr"/>
-      <c r="AH10" s="4" t="inlineStr"/>
-      <c r="AI10" s="4" t="inlineStr"/>
-      <c r="AJ10" s="4" t="inlineStr"/>
-      <c r="AK10" s="4" t="inlineStr"/>
-      <c r="AL10" s="4" t="inlineStr"/>
-      <c r="AM10" s="4" t="inlineStr"/>
-      <c r="AN10" s="4" t="inlineStr"/>
-      <c r="AO10" s="4" t="inlineStr"/>
-      <c r="AP10" s="4" t="inlineStr"/>
-      <c r="AQ10" s="4" t="inlineStr"/>
-      <c r="AR10" s="4" t="inlineStr"/>
-      <c r="AS10" s="4" t="inlineStr"/>
-      <c r="AT10" s="4" t="inlineStr"/>
-      <c r="AU10" s="4" t="inlineStr"/>
-      <c r="AV10" s="4" t="inlineStr"/>
-      <c r="AW10" s="4" t="inlineStr">
+      <c r="AP10" s="3" t="inlineStr"/>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr"/>
+      <c r="AS10" s="3" t="inlineStr"/>
+      <c r="AT10" s="3" t="inlineStr"/>
+      <c r="AU10" s="3" t="inlineStr"/>
+      <c r="AV10" s="3" t="inlineStr"/>
+      <c r="AW10" s="3" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX10" s="4" t="inlineStr"/>
-      <c r="AY10" s="4" t="inlineStr"/>
-      <c r="AZ10" s="4" t="inlineStr"/>
-      <c r="BA10" s="4" t="inlineStr"/>
-      <c r="BB10" s="4" t="inlineStr">
+      <c r="AX10" s="3" t="inlineStr"/>
+      <c r="AY10" s="3" t="inlineStr"/>
+      <c r="AZ10" s="3" t="inlineStr"/>
+      <c r="BA10" s="3" t="inlineStr"/>
+      <c r="BB10" s="3" t="inlineStr">
         <is>
           <t>WMT</t>
         </is>
       </c>
-      <c r="BC10" s="4" t="inlineStr">
+      <c r="BC10" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD10" s="4" t="inlineStr"/>
-      <c r="BE10" s="4" t="inlineStr">
+      <c r="BD10" s="3" t="inlineStr"/>
+      <c r="BE10" s="3" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
         </is>
       </c>
-      <c r="BF10" s="4" t="inlineStr">
+      <c r="BF10" s="3" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.654565+00:00</t>
         </is>
       </c>
-      <c r="BG10" s="4" t="inlineStr">
+      <c r="BG10" s="3" t="inlineStr">
         <is>
           <t>交易所目前名單</t>
         </is>
       </c>
-      <c r="BH10" s="4" t="inlineStr"/>
+      <c r="BH10" s="3" t="inlineStr"/>
+      <c r="BI10" s="3" t="inlineStr"/>
+      <c r="BJ10" s="3" t="inlineStr"/>
+      <c r="BK10" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>META</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Meta Platforms, Inc.</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>2026-08-30T02:43:55+08:00</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="3" t="inlineStr">
         <is>
           <t>Meta settlement reached: Ohio to receive over $300 million</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr"/>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>監管裁罰</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L11" s="4" t="inlineStr"/>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>0.477</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr"/>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNd3NOV2txR1JmNTdqNVkzS2drb0FIT2VJejhXY2g0N2daR3draDYyQnhwSWZHTEc0enI1WWJJVThEMXR5LXRmMVVXTkM4THJxY0pYelJNWm1KMDV2b254LVpmVjllTzBiMkZBVm80X0xqbmQxejRoTk1ZU3hGNEdMSk5iR21mNGFxb0t6d0ZTV1FlNTk30gGaAUFVX3lxTE5WQnY0WFRCMVNYMzJ5cFZQbWJiSHlaSjl6ZWE5UjQ1b1lRTmVJUzdPR2o4RnNIT1hVWVFQRWZNX2NDZDNBYW9wYjJCRjN5cUxMUnhqYzcwblAtLVBzZDBLQ0RMM21OcGdRUnhSMnFvMFNzUHZkT2gtdnNtZGFsazFoNnp4aXBHODAtZ0dWa2NqNmlMeFVZM2NFbGc?oc=5</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>wowktv.com</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr"/>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr"/>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>da1bf98cf9434f68ad3adae04e6c1eda</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>00ddd35c976af54ffba6bbe2</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr">
+        <is>
+          <t>209a279dda6945a064db3e7e</t>
+        </is>
+      </c>
+      <c r="AE11" s="3" t="inlineStr"/>
+      <c r="AF11" s="3" t="inlineStr"/>
+      <c r="AG11" s="3" t="inlineStr"/>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr"/>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr"/>
+      <c r="AM11" s="3" t="inlineStr"/>
+      <c r="AN11" s="3" t="inlineStr"/>
+      <c r="AO11" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O11" s="4" t="inlineStr">
-        <is>
-          <t>0.477</t>
-        </is>
-      </c>
-      <c r="P11" s="4" t="inlineStr"/>
-      <c r="Q11" s="4" t="inlineStr"/>
-      <c r="R11" s="4" t="inlineStr"/>
-      <c r="S11" s="4" t="inlineStr"/>
-      <c r="T11" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U11" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNd3NOV2txR1JmNTdqNVkzS2drb0FIT2VJejhXY2g0N2daR3draDYyQnhwSWZHTEc0enI1WWJJVThEMXR5LXRmMVVXTkM4THJxY0pYelJNWm1KMDV2b254LVpmVjllTzBiMkZBVm80X0xqbmQxejRoTk1ZU3hGNEdMSk5iR21mNGFxb0t6d0ZTV1FlNTk30gGaAUFVX3lxTE5WQnY0WFRCMVNYMzJ5cFZQbWJiSHlaSjl6ZWE5UjQ1b1lRTmVJUzdPR2o4RnNIT1hVWVFQRWZNX2NDZDNBYW9wYjJCRjN5cUxMUnhqYzcwblAtLVBzZDBLQ0RMM21OcGdRUnhSMnFvMFNzUHZkT2gtdnNtZGFsazFoNnp4aXBHODAtZ0dWa2NqNmlMeFVZM2NFbGc?oc=5</t>
-        </is>
-      </c>
-      <c r="V11" s="4" t="inlineStr">
-        <is>
-          <t>wowktv.com</t>
-        </is>
-      </c>
-      <c r="W11" s="4" t="inlineStr"/>
-      <c r="X11" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y11" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z11" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA11" s="4" t="inlineStr"/>
-      <c r="AB11" s="4" t="inlineStr"/>
-      <c r="AC11" s="4" t="inlineStr">
-        <is>
-          <t>00ddd35c976af54ffba6bbe2</t>
-        </is>
-      </c>
-      <c r="AD11" s="4" t="inlineStr">
-        <is>
-          <t>209a279dda6945a064db3e7e</t>
-        </is>
-      </c>
-      <c r="AE11" s="4" t="inlineStr"/>
-      <c r="AF11" s="4" t="inlineStr"/>
-      <c r="AG11" s="4" t="inlineStr"/>
-      <c r="AH11" s="4" t="inlineStr"/>
-      <c r="AI11" s="4" t="inlineStr"/>
-      <c r="AJ11" s="4" t="inlineStr"/>
-      <c r="AK11" s="4" t="inlineStr"/>
-      <c r="AL11" s="4" t="inlineStr"/>
-      <c r="AM11" s="4" t="inlineStr"/>
-      <c r="AN11" s="4" t="inlineStr"/>
-      <c r="AO11" s="4" t="inlineStr"/>
-      <c r="AP11" s="4" t="inlineStr"/>
-      <c r="AQ11" s="4" t="inlineStr"/>
-      <c r="AR11" s="4" t="inlineStr"/>
-      <c r="AS11" s="4" t="inlineStr"/>
-      <c r="AT11" s="4" t="inlineStr"/>
-      <c r="AU11" s="4" t="inlineStr"/>
-      <c r="AV11" s="4" t="inlineStr"/>
-      <c r="AW11" s="4" t="inlineStr">
+      <c r="AP11" s="3" t="inlineStr"/>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr"/>
+      <c r="AS11" s="3" t="inlineStr"/>
+      <c r="AT11" s="3" t="inlineStr"/>
+      <c r="AU11" s="3" t="inlineStr"/>
+      <c r="AV11" s="3" t="inlineStr"/>
+      <c r="AW11" s="3" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX11" s="4" t="inlineStr"/>
-      <c r="AY11" s="4" t="inlineStr"/>
-      <c r="AZ11" s="4" t="inlineStr"/>
-      <c r="BA11" s="4" t="inlineStr"/>
-      <c r="BB11" s="4" t="inlineStr">
+      <c r="AX11" s="3" t="inlineStr"/>
+      <c r="AY11" s="3" t="inlineStr"/>
+      <c r="AZ11" s="3" t="inlineStr"/>
+      <c r="BA11" s="3" t="inlineStr"/>
+      <c r="BB11" s="3" t="inlineStr">
         <is>
           <t>META</t>
         </is>
       </c>
-      <c r="BC11" s="4" t="inlineStr">
+      <c r="BC11" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD11" s="4" t="inlineStr"/>
-      <c r="BE11" s="4" t="inlineStr">
+      <c r="BD11" s="3" t="inlineStr"/>
+      <c r="BE11" s="3" t="inlineStr">
         <is>
           <t>https://investor.atmeta.com/stock-info/default.aspx</t>
         </is>
       </c>
-      <c r="BF11" s="4" t="inlineStr">
+      <c r="BF11" s="3" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="BG11" s="4" t="inlineStr">
+      <c r="BG11" s="3" t="inlineStr">
         <is>
           <t>上市公司</t>
         </is>
       </c>
-      <c r="BH11" s="4" t="inlineStr"/>
+      <c r="BH11" s="3" t="inlineStr"/>
+      <c r="BI11" s="3" t="inlineStr"/>
+      <c r="BJ11" s="3" t="inlineStr"/>
+      <c r="BK11" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL11" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>COO</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>Cooper Companies (The)</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>2026-08-30T00:37:26+08:00</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>Nike Installs Former Foot Locker Supply Chain Chief as Converse COO</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>供應鏈中斷</t>
         </is>
       </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、加入觀察</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="K12" s="4" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L12" s="5" t="inlineStr"/>
-      <c r="M12" s="5" t="inlineStr">
+      <c r="L12" s="4" t="inlineStr"/>
+      <c r="M12" s="4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N12" s="5" t="inlineStr">
+      <c r="N12" s="4" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O12" s="5" t="inlineStr">
+      <c r="O12" s="4" t="inlineStr">
         <is>
           <t>0.039</t>
         </is>
       </c>
-      <c r="P12" s="5" t="inlineStr"/>
-      <c r="Q12" s="5" t="inlineStr"/>
-      <c r="R12" s="5" t="inlineStr"/>
-      <c r="S12" s="5" t="inlineStr"/>
-      <c r="T12" s="5" t="inlineStr">
+      <c r="P12" s="4" t="inlineStr"/>
+      <c r="Q12" s="4" t="inlineStr"/>
+      <c r="R12" s="4" t="inlineStr"/>
+      <c r="S12" s="4" t="inlineStr"/>
+      <c r="T12" s="4" t="inlineStr">
         <is>
           <t>公司清單／別名核對</t>
         </is>
       </c>
-      <c r="U12" s="5" t="inlineStr">
+      <c r="U12" s="4" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQWDdCbklQanBQMkJ1YXBzR3hWNnlHM1B5ZU5aMDk3ZGpYR0o4X3IzN09WZDNNbmVLRUt1UHBBX1hxRTJoM2J3WE9EenZpT2pkeHZBekdwdlZmekhwaE9tMjlsRFI3WVFsTzdQbmZ2ZHg3QWhsZUYwWlhPRTQ1WEhSVzJHM1hvMlE4UVc1eEdVUElxSHh0SUozVw?oc=5</t>
         </is>
       </c>
-      <c r="V12" s="5" t="inlineStr">
+      <c r="V12" s="4" t="inlineStr">
         <is>
           <t>WWD</t>
         </is>
       </c>
-      <c r="W12" s="5" t="inlineStr"/>
-      <c r="X12" s="5" t="inlineStr">
+      <c r="W12" s="4" t="inlineStr"/>
+      <c r="X12" s="4" t="inlineStr">
         <is>
           <t>OPERATIONS</t>
         </is>
       </c>
-      <c r="Y12" s="5" t="inlineStr">
+      <c r="Y12" s="4" t="inlineStr">
         <is>
           <t>SUPPLY_CHAIN_DISRUPTION</t>
         </is>
       </c>
-      <c r="Z12" s="5" t="inlineStr">
+      <c r="Z12" s="4" t="inlineStr">
         <is>
           <t>supply chain</t>
         </is>
       </c>
-      <c r="AA12" s="5" t="inlineStr"/>
-      <c r="AB12" s="5" t="inlineStr"/>
-      <c r="AC12" s="5" t="inlineStr">
+      <c r="AA12" s="4" t="inlineStr"/>
+      <c r="AB12" s="4" t="inlineStr"/>
+      <c r="AC12" s="4" t="inlineStr">
         <is>
           <t>dc32a9237e8ca9638b26d5ec</t>
         </is>
       </c>
-      <c r="AD12" s="5" t="inlineStr">
+      <c r="AD12" s="4" t="inlineStr">
         <is>
           <t>1f273c467c5ad0509a9b6b04</t>
         </is>
       </c>
-      <c r="AE12" s="5" t="inlineStr"/>
-      <c r="AF12" s="5" t="inlineStr"/>
-      <c r="AG12" s="5" t="inlineStr"/>
-      <c r="AH12" s="5" t="inlineStr"/>
-      <c r="AI12" s="5" t="inlineStr"/>
-      <c r="AJ12" s="5" t="inlineStr"/>
-      <c r="AK12" s="5" t="inlineStr"/>
-      <c r="AL12" s="5" t="inlineStr"/>
-      <c r="AM12" s="5" t="inlineStr"/>
-      <c r="AN12" s="5" t="inlineStr"/>
-      <c r="AO12" s="5" t="inlineStr"/>
-      <c r="AP12" s="5" t="inlineStr"/>
-      <c r="AQ12" s="5" t="inlineStr"/>
-      <c r="AR12" s="5" t="inlineStr"/>
-      <c r="AS12" s="5" t="inlineStr"/>
-      <c r="AT12" s="5" t="inlineStr"/>
-      <c r="AU12" s="5" t="inlineStr"/>
-      <c r="AV12" s="5" t="inlineStr"/>
-      <c r="AW12" s="5" t="inlineStr"/>
-      <c r="AX12" s="5" t="inlineStr"/>
-      <c r="AY12" s="5" t="inlineStr"/>
-      <c r="AZ12" s="5" t="inlineStr"/>
-      <c r="BA12" s="5" t="inlineStr"/>
-      <c r="BB12" s="5" t="inlineStr">
+      <c r="AE12" s="4" t="inlineStr"/>
+      <c r="AF12" s="4" t="inlineStr"/>
+      <c r="AG12" s="4" t="inlineStr"/>
+      <c r="AH12" s="4" t="inlineStr"/>
+      <c r="AI12" s="4" t="inlineStr"/>
+      <c r="AJ12" s="4" t="inlineStr"/>
+      <c r="AK12" s="4" t="inlineStr"/>
+      <c r="AL12" s="4" t="inlineStr"/>
+      <c r="AM12" s="4" t="inlineStr"/>
+      <c r="AN12" s="4" t="inlineStr"/>
+      <c r="AO12" s="4" t="inlineStr"/>
+      <c r="AP12" s="4" t="inlineStr"/>
+      <c r="AQ12" s="4" t="inlineStr"/>
+      <c r="AR12" s="4" t="inlineStr"/>
+      <c r="AS12" s="4" t="inlineStr"/>
+      <c r="AT12" s="4" t="inlineStr"/>
+      <c r="AU12" s="4" t="inlineStr"/>
+      <c r="AV12" s="4" t="inlineStr"/>
+      <c r="AW12" s="4" t="inlineStr"/>
+      <c r="AX12" s="4" t="inlineStr"/>
+      <c r="AY12" s="4" t="inlineStr"/>
+      <c r="AZ12" s="4" t="inlineStr"/>
+      <c r="BA12" s="4" t="inlineStr"/>
+      <c r="BB12" s="4" t="inlineStr">
         <is>
           <t>COO</t>
         </is>
       </c>
-      <c r="BC12" s="5" t="inlineStr">
+      <c r="BC12" s="4" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD12" s="5" t="inlineStr"/>
-      <c r="BE12" s="5" t="inlineStr">
+      <c r="BD12" s="4" t="inlineStr"/>
+      <c r="BE12" s="4" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF12" s="5" t="inlineStr"/>
-      <c r="BG12" s="5" t="inlineStr">
+      <c r="BF12" s="4" t="inlineStr"/>
+      <c r="BG12" s="4" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH12" s="5" t="inlineStr"/>
+      <c r="BH12" s="4" t="inlineStr"/>
+      <c r="BI12" s="4" t="inlineStr"/>
+      <c r="BJ12" s="4" t="inlineStr"/>
+      <c r="BK12" s="4" t="inlineStr"/>
+      <c r="BL12" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH12"/>
+  <autoFilter ref="A1:BL12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2708,7 +2868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH7"/>
+  <dimension ref="A1:BL6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2771,6 +2931,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3074,6 +3238,26 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -3105,12 +3289,12 @@
       <c r="G2" s="3" t="inlineStr"/>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>違約</t>
+          <t>重大訴訟</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
@@ -3120,17 +3304,17 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="3" t="inlineStr">
@@ -3166,7 +3350,7 @@
       </c>
       <c r="Y2" s="3" t="inlineStr">
         <is>
-          <t>DEFAULT</t>
+          <t>MAJOR_LITIGATION</t>
         </is>
       </c>
       <c r="Z2" s="3" t="inlineStr">
@@ -3175,7 +3359,11 @@
         </is>
       </c>
       <c r="AA2" s="3" t="inlineStr"/>
-      <c r="AB2" s="3" t="inlineStr"/>
+      <c r="AB2" s="3" t="inlineStr">
+        <is>
+          <t>c90316d5cd9f4f858e19e3d703fc4cb5</t>
+        </is>
+      </c>
       <c r="AC2" s="3" t="inlineStr">
         <is>
           <t>7210521af56fdba6a7b60a22</t>
@@ -3198,7 +3386,7 @@
       <c r="AN2" s="3" t="inlineStr"/>
       <c r="AO2" s="3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP2" s="3" t="inlineStr"/>
@@ -3240,516 +3428,604 @@
       </c>
       <c r="BG2" s="3" t="inlineStr"/>
       <c r="BH2" s="3" t="inlineStr"/>
+      <c r="BI2" s="3" t="inlineStr">
+        <is>
+          <t>Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ2" s="3" t="inlineStr"/>
+      <c r="BK2" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:43:17.016263+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>EFX</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>Equifax, Inc. Common Stock</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-30T15:37:01+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>Did Equifax's (EFX) Dividend Steadiness and Legal Settlement Proposal Just Reframe Its Risk‑Reward Profile?</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr"/>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-30T15:00:00+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>This week's Meta settlement will reverberate across the world for years</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>監管裁罰</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="4" t="inlineStr"/>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>0.099</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE5wWHRSVFl5ZHFlR1NwYmJwNDNld1l1d3ZLS19wZU9aYjFlY1RYZWpBWFN0c3Q4YmN3dHlUWlRSY25nMFR6S3Azb1A2ci1tbjE3VkVZV2FqNHpmc1hnQkVhQldwcmk?oc=5</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>Tech Policy Press</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr"/>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr"/>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>ac8a9ef184c544b788e8cf2469746289</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>ed2de18d801507fb35a62f33</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr">
+        <is>
+          <t>edbb4144ee531b884bbb6c3d</t>
+        </is>
+      </c>
+      <c r="AE3" s="3" t="inlineStr"/>
+      <c r="AF3" s="3" t="inlineStr"/>
+      <c r="AG3" s="3" t="inlineStr"/>
+      <c r="AH3" s="3" t="inlineStr"/>
+      <c r="AI3" s="3" t="inlineStr"/>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr"/>
+      <c r="AM3" s="3" t="inlineStr"/>
+      <c r="AN3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O3" s="4" t="inlineStr">
-        <is>
-          <t>0.204</t>
-        </is>
-      </c>
-      <c r="P3" s="4" t="inlineStr"/>
-      <c r="Q3" s="4" t="inlineStr"/>
-      <c r="R3" s="4" t="inlineStr"/>
-      <c r="S3" s="4" t="inlineStr"/>
-      <c r="T3" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U3" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxQNGpnZ2lNck9WMTA5VG4wajJoU05HdFdqTHhGYkZ0QXdybnBPZEFMcVdmTDBKbHV3VVRiRGtKRkRHZWM4SDNubGFLelc4S2laQXV0WHZscmNrSVgxLWlMUGFOQmtGRDZsTDZwbFVkUU1KelRiWTc2czJmYTBmS250MWVITGpzalVObVdsMkd6dmZfTVRoemtWTXZ5alJkcDIzY0FEdU9GUU1CXzI0NTd4YlRFSkpFWThSRXdjQ2hIRlkzVkVjUUdzNUNOYjZ0enPSAdQBQVVfeXFMTkwyS2FESkhtLWFCTktzTmsyVXN4akc4djVTVG51STVlMHctVUNVUm5LTG90NXpLbTZkVnU4T3F3UnNiZ0R5RjkweUkzcl9ZZDc1bVBWMlhyVjhsTEtNanhUNENTSl9mUUN2SFpCMWlmRVZidVFPN1gzQXNZelpCSS1iVURNLS1YczBLT0psNEZib0FoVGViV0JwMGt4dXZld2RCZFRNNEFMMkZINElxYmZ4MllyWUw1bHRsYmlOaktwZTA2OV9YX3JwNjA3NHdPLU1sY1Y?oc=5</t>
-        </is>
-      </c>
-      <c r="V3" s="4" t="inlineStr">
-        <is>
-          <t>simplywall.st</t>
-        </is>
-      </c>
-      <c r="W3" s="4" t="inlineStr"/>
-      <c r="X3" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y3" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z3" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA3" s="4" t="inlineStr"/>
-      <c r="AB3" s="4" t="inlineStr"/>
-      <c r="AC3" s="4" t="inlineStr">
-        <is>
-          <t>4df3441d339fa556fbe78fd4</t>
-        </is>
-      </c>
-      <c r="AD3" s="4" t="inlineStr">
-        <is>
-          <t>9171d3d5d6a05bdc43f8277c</t>
-        </is>
-      </c>
-      <c r="AE3" s="4" t="inlineStr"/>
-      <c r="AF3" s="4" t="inlineStr"/>
-      <c r="AG3" s="4" t="inlineStr"/>
-      <c r="AH3" s="4" t="inlineStr"/>
-      <c r="AI3" s="4" t="inlineStr"/>
-      <c r="AJ3" s="4" t="inlineStr"/>
-      <c r="AK3" s="4" t="inlineStr"/>
-      <c r="AL3" s="4" t="inlineStr"/>
-      <c r="AM3" s="4" t="inlineStr"/>
-      <c r="AN3" s="4" t="inlineStr"/>
-      <c r="AO3" s="4" t="inlineStr"/>
-      <c r="AP3" s="4" t="inlineStr"/>
-      <c r="AQ3" s="4" t="inlineStr"/>
-      <c r="AR3" s="4" t="inlineStr"/>
-      <c r="AS3" s="4" t="inlineStr"/>
-      <c r="AT3" s="4" t="inlineStr"/>
-      <c r="AU3" s="4" t="inlineStr"/>
-      <c r="AV3" s="4" t="inlineStr"/>
-      <c r="AW3" s="4" t="inlineStr">
-        <is>
-          <t>NYSE</t>
-        </is>
-      </c>
-      <c r="AX3" s="4" t="inlineStr"/>
-      <c r="AY3" s="4" t="inlineStr"/>
-      <c r="AZ3" s="4" t="inlineStr"/>
-      <c r="BA3" s="4" t="inlineStr"/>
-      <c r="BB3" s="4" t="inlineStr">
-        <is>
-          <t>EFX</t>
-        </is>
-      </c>
-      <c r="BC3" s="4" t="inlineStr">
+      <c r="AP3" s="3" t="inlineStr"/>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr"/>
+      <c r="AS3" s="3" t="inlineStr"/>
+      <c r="AT3" s="3" t="inlineStr"/>
+      <c r="AU3" s="3" t="inlineStr"/>
+      <c r="AV3" s="3" t="inlineStr"/>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>NASDAQ</t>
+        </is>
+      </c>
+      <c r="AX3" s="3" t="inlineStr"/>
+      <c r="AY3" s="3" t="inlineStr"/>
+      <c r="AZ3" s="3" t="inlineStr"/>
+      <c r="BA3" s="3" t="inlineStr"/>
+      <c r="BB3" s="3" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="BC3" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD3" s="4" t="inlineStr"/>
-      <c r="BE3" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF3" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG3" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH3" s="4" t="inlineStr"/>
+      <c r="BD3" s="3" t="inlineStr"/>
+      <c r="BE3" s="3" t="inlineStr">
+        <is>
+          <t>https://investor.atmeta.com/stock-info/default.aspx</t>
+        </is>
+      </c>
+      <c r="BF3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="BG3" s="3" t="inlineStr">
+        <is>
+          <t>上市公司</t>
+        </is>
+      </c>
+      <c r="BH3" s="3" t="inlineStr"/>
+      <c r="BI3" s="3" t="inlineStr"/>
+      <c r="BJ3" s="3" t="inlineStr"/>
+      <c r="BK3" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Meta Platforms, Inc.</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-30T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>This week's Meta settlement will reverberate across the world for years</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>WMT</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Walmart Inc.</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-30T05:24:49+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Walmart agrees to pay $50M settlement over allegations its pharmacies filled illegal opioid prescriptions</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>監管裁罰</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr"/>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>'-0.678</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr"/>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxNUDNOU2xVQXUtM3NYR0t2VFZ1ckV1QjBlYzBnVFVYYmZPeE91bUlvT0FKZ1haUkZzUVFPMExfWVpPS2syUWxPenJ6bGczRUd2UHFMRHh3R2pRa2VoRjZyNG91RUc0dmF1amU4NFB0ZW5TcFFhMDU4T1RaX3lOVE5oRHJ1enNVOXJiSk5LNkprWUZleXpydDhjRVRxRk14Nl9HRXZUajBPTlphT2tpcnk5WWNFdklRQnJpWGE0NTJMb1JfVkF1QWRLYjF6SFgyZw?oc=5</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>FOX 7 Austin</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr"/>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr"/>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>7a2d3908ea6049d993fd4df901a2530b</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>5f8fefd1073085060d66d2a3</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr">
+        <is>
+          <t>66ab313c9e99b9661237f750</t>
+        </is>
+      </c>
+      <c r="AE4" s="3" t="inlineStr"/>
+      <c r="AF4" s="3" t="inlineStr"/>
+      <c r="AG4" s="3" t="inlineStr"/>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr"/>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr"/>
+      <c r="AM4" s="3" t="inlineStr"/>
+      <c r="AN4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
-          <t>0.099</t>
-        </is>
-      </c>
-      <c r="P4" s="4" t="inlineStr"/>
-      <c r="Q4" s="4" t="inlineStr"/>
-      <c r="R4" s="4" t="inlineStr"/>
-      <c r="S4" s="4" t="inlineStr"/>
-      <c r="T4" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U4" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE5wWHRSVFl5ZHFlR1NwYmJwNDNld1l1d3ZLS19wZU9aYjFlY1RYZWpBWFN0c3Q4YmN3dHlUWlRSY25nMFR6S3Azb1A2ci1tbjE3VkVZV2FqNHpmc1hnQkVhQldwcmk?oc=5</t>
-        </is>
-      </c>
-      <c r="V4" s="4" t="inlineStr">
-        <is>
-          <t>Tech Policy Press</t>
-        </is>
-      </c>
-      <c r="W4" s="4" t="inlineStr"/>
-      <c r="X4" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y4" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z4" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA4" s="4" t="inlineStr"/>
-      <c r="AB4" s="4" t="inlineStr"/>
-      <c r="AC4" s="4" t="inlineStr">
-        <is>
-          <t>ed2de18d801507fb35a62f33</t>
-        </is>
-      </c>
-      <c r="AD4" s="4" t="inlineStr">
-        <is>
-          <t>edbb4144ee531b884bbb6c3d</t>
-        </is>
-      </c>
-      <c r="AE4" s="4" t="inlineStr"/>
-      <c r="AF4" s="4" t="inlineStr"/>
-      <c r="AG4" s="4" t="inlineStr"/>
-      <c r="AH4" s="4" t="inlineStr"/>
-      <c r="AI4" s="4" t="inlineStr"/>
-      <c r="AJ4" s="4" t="inlineStr"/>
-      <c r="AK4" s="4" t="inlineStr"/>
-      <c r="AL4" s="4" t="inlineStr"/>
-      <c r="AM4" s="4" t="inlineStr"/>
-      <c r="AN4" s="4" t="inlineStr"/>
-      <c r="AO4" s="4" t="inlineStr"/>
-      <c r="AP4" s="4" t="inlineStr"/>
-      <c r="AQ4" s="4" t="inlineStr"/>
-      <c r="AR4" s="4" t="inlineStr"/>
-      <c r="AS4" s="4" t="inlineStr"/>
-      <c r="AT4" s="4" t="inlineStr"/>
-      <c r="AU4" s="4" t="inlineStr"/>
-      <c r="AV4" s="4" t="inlineStr"/>
-      <c r="AW4" s="4" t="inlineStr">
+      <c r="AP4" s="3" t="inlineStr"/>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr"/>
+      <c r="AS4" s="3" t="inlineStr"/>
+      <c r="AT4" s="3" t="inlineStr"/>
+      <c r="AU4" s="3" t="inlineStr"/>
+      <c r="AV4" s="3" t="inlineStr"/>
+      <c r="AW4" s="3" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX4" s="4" t="inlineStr"/>
-      <c r="AY4" s="4" t="inlineStr"/>
-      <c r="AZ4" s="4" t="inlineStr"/>
-      <c r="BA4" s="4" t="inlineStr"/>
-      <c r="BB4" s="4" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="BC4" s="4" t="inlineStr">
+      <c r="AX4" s="3" t="inlineStr"/>
+      <c r="AY4" s="3" t="inlineStr"/>
+      <c r="AZ4" s="3" t="inlineStr"/>
+      <c r="BA4" s="3" t="inlineStr"/>
+      <c r="BB4" s="3" t="inlineStr">
+        <is>
+          <t>WMT</t>
+        </is>
+      </c>
+      <c r="BC4" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD4" s="4" t="inlineStr"/>
-      <c r="BE4" s="4" t="inlineStr">
-        <is>
-          <t>https://investor.atmeta.com/stock-info/default.aspx</t>
-        </is>
-      </c>
-      <c r="BF4" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="BG4" s="4" t="inlineStr">
-        <is>
-          <t>上市公司</t>
-        </is>
-      </c>
-      <c r="BH4" s="4" t="inlineStr"/>
+      <c r="BD4" s="3" t="inlineStr"/>
+      <c r="BE4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
+        </is>
+      </c>
+      <c r="BF4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:15:41.654565+00:00</t>
+        </is>
+      </c>
+      <c r="BG4" s="3" t="inlineStr">
+        <is>
+          <t>交易所目前名單</t>
+        </is>
+      </c>
+      <c r="BH4" s="3" t="inlineStr"/>
+      <c r="BI4" s="3" t="inlineStr"/>
+      <c r="BJ4" s="3" t="inlineStr"/>
+      <c r="BK4" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>WMT</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Walmart Inc.</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-30T05:24:49+08:00</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Walmart agrees to pay $50M settlement over allegations its pharmacies filled illegal opioid prescriptions</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Meta Platforms, Inc.</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-30T02:43:55+08:00</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Meta settlement reached: Ohio to receive over $300 million</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>監管裁罰</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>通知、檢視授信及自營部位、持續追蹤</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>0.477</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNd3NOV2txR1JmNTdqNVkzS2drb0FIT2VJejhXY2g0N2daR3draDYyQnhwSWZHTEc0enI1WWJJVThEMXR5LXRmMVVXTkM4THJxY0pYelJNWm1KMDV2b254LVpmVjllTzBiMkZBVm80X0xqbmQxejRoTk1ZU3hGNEdMSk5iR21mNGFxb0t6d0ZTV1FlNTk30gGaAUFVX3lxTE5WQnY0WFRCMVNYMzJ5cFZQbWJiSHlaSjl6ZWE5UjQ1b1lRTmVJUzdPR2o4RnNIT1hVWVFQRWZNX2NDZDNBYW9wYjJCRjN5cUxMUnhqYzcwblAtLVBzZDBLQ0RMM21OcGdRUnhSMnFvMFNzUHZkT2gtdnNtZGFsazFoNnp4aXBHODAtZ0dWa2NqNmlMeFVZM2NFbGc?oc=5</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>wowktv.com</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr"/>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>LEGAL</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>REGULATORY_PENALTY</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr"/>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>da1bf98cf9434f68ad3adae04e6c1eda</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>00ddd35c976af54ffba6bbe2</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr">
+        <is>
+          <t>209a279dda6945a064db3e7e</t>
+        </is>
+      </c>
+      <c r="AE5" s="3" t="inlineStr"/>
+      <c r="AF5" s="3" t="inlineStr"/>
+      <c r="AG5" s="3" t="inlineStr"/>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr"/>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr"/>
+      <c r="AM5" s="3" t="inlineStr"/>
+      <c r="AN5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O5" s="4" t="inlineStr">
-        <is>
-          <t>'-0.678</t>
-        </is>
-      </c>
-      <c r="P5" s="4" t="inlineStr"/>
-      <c r="Q5" s="4" t="inlineStr"/>
-      <c r="R5" s="4" t="inlineStr"/>
-      <c r="S5" s="4" t="inlineStr"/>
-      <c r="T5" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U5" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxNUDNOU2xVQXUtM3NYR0t2VFZ1ckV1QjBlYzBnVFVYYmZPeE91bUlvT0FKZ1haUkZzUVFPMExfWVpPS2syUWxPenJ6bGczRUd2UHFMRHh3R2pRa2VoRjZyNG91RUc0dmF1amU4NFB0ZW5TcFFhMDU4T1RaX3lOVE5oRHJ1enNVOXJiSk5LNkprWUZleXpydDhjRVRxRk14Nl9HRXZUajBPTlphT2tpcnk5WWNFdklRQnJpWGE0NTJMb1JfVkF1QWRLYjF6SFgyZw?oc=5</t>
-        </is>
-      </c>
-      <c r="V5" s="4" t="inlineStr">
-        <is>
-          <t>FOX 7 Austin</t>
-        </is>
-      </c>
-      <c r="W5" s="4" t="inlineStr"/>
-      <c r="X5" s="4" t="inlineStr">
-        <is>
-          <t>LEGAL</t>
-        </is>
-      </c>
-      <c r="Y5" s="4" t="inlineStr">
-        <is>
-          <t>REGULATORY_PENALTY</t>
-        </is>
-      </c>
-      <c r="Z5" s="4" t="inlineStr">
-        <is>
-          <t>settlement</t>
-        </is>
-      </c>
-      <c r="AA5" s="4" t="inlineStr"/>
-      <c r="AB5" s="4" t="inlineStr"/>
-      <c r="AC5" s="4" t="inlineStr">
-        <is>
-          <t>5f8fefd1073085060d66d2a3</t>
-        </is>
-      </c>
-      <c r="AD5" s="4" t="inlineStr">
-        <is>
-          <t>66ab313c9e99b9661237f750</t>
-        </is>
-      </c>
-      <c r="AE5" s="4" t="inlineStr"/>
-      <c r="AF5" s="4" t="inlineStr"/>
-      <c r="AG5" s="4" t="inlineStr"/>
-      <c r="AH5" s="4" t="inlineStr"/>
-      <c r="AI5" s="4" t="inlineStr"/>
-      <c r="AJ5" s="4" t="inlineStr"/>
-      <c r="AK5" s="4" t="inlineStr"/>
-      <c r="AL5" s="4" t="inlineStr"/>
-      <c r="AM5" s="4" t="inlineStr"/>
-      <c r="AN5" s="4" t="inlineStr"/>
-      <c r="AO5" s="4" t="inlineStr"/>
-      <c r="AP5" s="4" t="inlineStr"/>
-      <c r="AQ5" s="4" t="inlineStr"/>
-      <c r="AR5" s="4" t="inlineStr"/>
-      <c r="AS5" s="4" t="inlineStr"/>
-      <c r="AT5" s="4" t="inlineStr"/>
-      <c r="AU5" s="4" t="inlineStr"/>
-      <c r="AV5" s="4" t="inlineStr"/>
-      <c r="AW5" s="4" t="inlineStr">
+      <c r="AP5" s="3" t="inlineStr"/>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr"/>
+      <c r="AS5" s="3" t="inlineStr"/>
+      <c r="AT5" s="3" t="inlineStr"/>
+      <c r="AU5" s="3" t="inlineStr"/>
+      <c r="AV5" s="3" t="inlineStr"/>
+      <c r="AW5" s="3" t="inlineStr">
         <is>
           <t>NASDAQ</t>
         </is>
       </c>
-      <c r="AX5" s="4" t="inlineStr"/>
-      <c r="AY5" s="4" t="inlineStr"/>
-      <c r="AZ5" s="4" t="inlineStr"/>
-      <c r="BA5" s="4" t="inlineStr"/>
-      <c r="BB5" s="4" t="inlineStr">
-        <is>
-          <t>WMT</t>
-        </is>
-      </c>
-      <c r="BC5" s="4" t="inlineStr">
+      <c r="AX5" s="3" t="inlineStr"/>
+      <c r="AY5" s="3" t="inlineStr"/>
+      <c r="AZ5" s="3" t="inlineStr"/>
+      <c r="BA5" s="3" t="inlineStr"/>
+      <c r="BB5" s="3" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="BC5" s="3" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD5" s="4" t="inlineStr"/>
-      <c r="BE5" s="4" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG5" s="4" t="inlineStr">
-        <is>
-          <t>交易所目前名單</t>
-        </is>
-      </c>
-      <c r="BH5" s="4" t="inlineStr"/>
+      <c r="BD5" s="3" t="inlineStr"/>
+      <c r="BE5" s="3" t="inlineStr">
+        <is>
+          <t>https://investor.atmeta.com/stock-info/default.aspx</t>
+        </is>
+      </c>
+      <c r="BF5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="BG5" s="3" t="inlineStr">
+        <is>
+          <t>上市公司</t>
+        </is>
+      </c>
+      <c r="BH5" s="3" t="inlineStr"/>
+      <c r="BI5" s="3" t="inlineStr"/>
+      <c r="BJ5" s="3" t="inlineStr"/>
+      <c r="BK5" s="3" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:42:35.885456+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -3764,38 +4040,38 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>COO</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Meta Platforms, Inc.</t>
+          <t>Cooper Companies (The)</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>2026-08-30T02:43:55+08:00</t>
+          <t>2026-08-30T00:37:26+08:00</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>Meta settlement reached: Ohio to receive over $300 million</t>
+          <t>Nike Installs Former Foot Locker Supply Chain Chief as Converse COO</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr"/>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>監管裁罰</t>
+          <t>供應鏈中斷</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
+          <t>通知、檢視授信及自營部位、加入觀察</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
@@ -3816,7 +4092,7 @@
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>0.477</t>
+          <t>0.039</t>
         </is>
       </c>
       <c r="P6" s="4" t="inlineStr"/>
@@ -3830,40 +4106,40 @@
       </c>
       <c r="U6" s="4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNd3NOV2txR1JmNTdqNVkzS2drb0FIT2VJejhXY2g0N2daR3draDYyQnhwSWZHTEc0enI1WWJJVThEMXR5LXRmMVVXTkM4THJxY0pYelJNWm1KMDV2b254LVpmVjllTzBiMkZBVm80X0xqbmQxejRoTk1ZU3hGNEdMSk5iR21mNGFxb0t6d0ZTV1FlNTk30gGaAUFVX3lxTE5WQnY0WFRCMVNYMzJ5cFZQbWJiSHlaSjl6ZWE5UjQ1b1lRTmVJUzdPR2o4RnNIT1hVWVFQRWZNX2NDZDNBYW9wYjJCRjN5cUxMUnhqYzcwblAtLVBzZDBLQ0RMM21OcGdRUnhSMnFvMFNzUHZkT2gtdnNtZGFsazFoNnp4aXBHODAtZ0dWa2NqNmlMeFVZM2NFbGc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQWDdCbklQanBQMkJ1YXBzR3hWNnlHM1B5ZU5aMDk3ZGpYR0o4X3IzN09WZDNNbmVLRUt1UHBBX1hxRTJoM2J3WE9EenZpT2pkeHZBekdwdlZmekhwaE9tMjlsRFI3WVFsTzdQbmZ2ZHg3QWhsZUYwWlhPRTQ1WEhSVzJHM1hvMlE4UVc1eEdVUElxSHh0SUozVw?oc=5</t>
         </is>
       </c>
       <c r="V6" s="4" t="inlineStr">
         <is>
-          <t>wowktv.com</t>
+          <t>WWD</t>
         </is>
       </c>
       <c r="W6" s="4" t="inlineStr"/>
       <c r="X6" s="4" t="inlineStr">
         <is>
-          <t>LEGAL</t>
+          <t>OPERATIONS</t>
         </is>
       </c>
       <c r="Y6" s="4" t="inlineStr">
         <is>
-          <t>REGULATORY_PENALTY</t>
+          <t>SUPPLY_CHAIN_DISRUPTION</t>
         </is>
       </c>
       <c r="Z6" s="4" t="inlineStr">
         <is>
-          <t>settlement</t>
+          <t>supply chain</t>
         </is>
       </c>
       <c r="AA6" s="4" t="inlineStr"/>
       <c r="AB6" s="4" t="inlineStr"/>
       <c r="AC6" s="4" t="inlineStr">
         <is>
-          <t>00ddd35c976af54ffba6bbe2</t>
+          <t>dc32a9237e8ca9638b26d5ec</t>
         </is>
       </c>
       <c r="AD6" s="4" t="inlineStr">
         <is>
-          <t>209a279dda6945a064db3e7e</t>
+          <t>1f273c467c5ad0509a9b6b04</t>
         </is>
       </c>
       <c r="AE6" s="4" t="inlineStr"/>
@@ -3884,18 +4160,14 @@
       <c r="AT6" s="4" t="inlineStr"/>
       <c r="AU6" s="4" t="inlineStr"/>
       <c r="AV6" s="4" t="inlineStr"/>
-      <c r="AW6" s="4" t="inlineStr">
-        <is>
-          <t>NASDAQ</t>
-        </is>
-      </c>
+      <c r="AW6" s="4" t="inlineStr"/>
       <c r="AX6" s="4" t="inlineStr"/>
       <c r="AY6" s="4" t="inlineStr"/>
       <c r="AZ6" s="4" t="inlineStr"/>
       <c r="BA6" s="4" t="inlineStr"/>
       <c r="BB6" s="4" t="inlineStr">
         <is>
-          <t>META</t>
+          <t>COO</t>
         </is>
       </c>
       <c r="BC6" s="4" t="inlineStr">
@@ -3906,185 +4178,23 @@
       <c r="BD6" s="4" t="inlineStr"/>
       <c r="BE6" s="4" t="inlineStr">
         <is>
-          <t>https://investor.atmeta.com/stock-info/default.aspx</t>
-        </is>
-      </c>
-      <c r="BF6" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
+          <t>公司清單</t>
+        </is>
+      </c>
+      <c r="BF6" s="4" t="inlineStr"/>
       <c r="BG6" s="4" t="inlineStr">
         <is>
-          <t>上市公司</t>
+          <t>公司清單／交易所參照</t>
         </is>
       </c>
       <c r="BH6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>COO</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Cooper Companies (The)</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-30T00:37:26+08:00</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>Nike Installs Former Foot Locker Supply Chain Chief as Converse COO</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr"/>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L7" s="5" t="inlineStr"/>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N7" s="5" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O7" s="5" t="inlineStr">
-        <is>
-          <t>0.039</t>
-        </is>
-      </c>
-      <c r="P7" s="5" t="inlineStr"/>
-      <c r="Q7" s="5" t="inlineStr"/>
-      <c r="R7" s="5" t="inlineStr"/>
-      <c r="S7" s="5" t="inlineStr"/>
-      <c r="T7" s="5" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U7" s="5" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQWDdCbklQanBQMkJ1YXBzR3hWNnlHM1B5ZU5aMDk3ZGpYR0o4X3IzN09WZDNNbmVLRUt1UHBBX1hxRTJoM2J3WE9EenZpT2pkeHZBekdwdlZmekhwaE9tMjlsRFI3WVFsTzdQbmZ2ZHg3QWhsZUYwWlhPRTQ1WEhSVzJHM1hvMlE4UVc1eEdVUElxSHh0SUozVw?oc=5</t>
-        </is>
-      </c>
-      <c r="V7" s="5" t="inlineStr">
-        <is>
-          <t>WWD</t>
-        </is>
-      </c>
-      <c r="W7" s="5" t="inlineStr"/>
-      <c r="X7" s="5" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y7" s="5" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z7" s="5" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA7" s="5" t="inlineStr"/>
-      <c r="AB7" s="5" t="inlineStr"/>
-      <c r="AC7" s="5" t="inlineStr">
-        <is>
-          <t>dc32a9237e8ca9638b26d5ec</t>
-        </is>
-      </c>
-      <c r="AD7" s="5" t="inlineStr">
-        <is>
-          <t>1f273c467c5ad0509a9b6b04</t>
-        </is>
-      </c>
-      <c r="AE7" s="5" t="inlineStr"/>
-      <c r="AF7" s="5" t="inlineStr"/>
-      <c r="AG7" s="5" t="inlineStr"/>
-      <c r="AH7" s="5" t="inlineStr"/>
-      <c r="AI7" s="5" t="inlineStr"/>
-      <c r="AJ7" s="5" t="inlineStr"/>
-      <c r="AK7" s="5" t="inlineStr"/>
-      <c r="AL7" s="5" t="inlineStr"/>
-      <c r="AM7" s="5" t="inlineStr"/>
-      <c r="AN7" s="5" t="inlineStr"/>
-      <c r="AO7" s="5" t="inlineStr"/>
-      <c r="AP7" s="5" t="inlineStr"/>
-      <c r="AQ7" s="5" t="inlineStr"/>
-      <c r="AR7" s="5" t="inlineStr"/>
-      <c r="AS7" s="5" t="inlineStr"/>
-      <c r="AT7" s="5" t="inlineStr"/>
-      <c r="AU7" s="5" t="inlineStr"/>
-      <c r="AV7" s="5" t="inlineStr"/>
-      <c r="AW7" s="5" t="inlineStr"/>
-      <c r="AX7" s="5" t="inlineStr"/>
-      <c r="AY7" s="5" t="inlineStr"/>
-      <c r="AZ7" s="5" t="inlineStr"/>
-      <c r="BA7" s="5" t="inlineStr"/>
-      <c r="BB7" s="5" t="inlineStr">
-        <is>
-          <t>COO</t>
-        </is>
-      </c>
-      <c r="BC7" s="5" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD7" s="5" t="inlineStr"/>
-      <c r="BE7" s="5" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF7" s="5" t="inlineStr"/>
-      <c r="BG7" s="5" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH7" s="5" t="inlineStr"/>
+      <c r="BI6" s="4" t="inlineStr"/>
+      <c r="BJ6" s="4" t="inlineStr"/>
+      <c r="BK6" s="4" t="inlineStr"/>
+      <c r="BL6" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH7"/>
+  <autoFilter ref="A1:BL6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4095,7 +4205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH3"/>
+  <dimension ref="A1:BL2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4158,6 +4268,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4461,345 +4575,203 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr"/>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Apple Inc.</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-30T19:26:03+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>蘋果Siri功能跳票賠17億</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr"/>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>違約</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>AT&amp;T</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-30T15:00:00+08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Don’t forget the trees during drought!</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>天災</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>僅紀錄</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>規則</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>待人工覆核</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>原有新聞流程</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr"/>
-      <c r="P2" s="3" t="inlineStr"/>
-      <c r="Q2" s="3" t="inlineStr"/>
-      <c r="R2" s="3" t="inlineStr"/>
-      <c r="S2" s="3" t="inlineStr"/>
-      <c r="T2" s="3" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>0.021</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="R2" s="2" t="inlineStr"/>
+      <c r="S2" s="2" t="inlineStr"/>
+      <c r="T2" s="2" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/live/2640938</t>
-        </is>
-      </c>
-      <c r="V2" s="3" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="inlineStr"/>
-      <c r="X2" s="3" t="inlineStr">
-        <is>
-          <t>FINANCIAL</t>
-        </is>
-      </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>DEFAULT</t>
-        </is>
-      </c>
-      <c r="Z2" s="3" t="inlineStr">
-        <is>
-          <t>跳票</t>
-        </is>
-      </c>
-      <c r="AA2" s="3" t="inlineStr"/>
-      <c r="AB2" s="3" t="inlineStr"/>
-      <c r="AC2" s="3" t="inlineStr">
-        <is>
-          <t>7210521af56fdba6a7b60a22</t>
-        </is>
-      </c>
-      <c r="AD2" s="3" t="inlineStr">
-        <is>
-          <t>e38e29eaf5c6faa3f5dcc44f</t>
-        </is>
-      </c>
-      <c r="AE2" s="3" t="inlineStr"/>
-      <c r="AF2" s="3" t="inlineStr"/>
-      <c r="AG2" s="3" t="inlineStr"/>
-      <c r="AH2" s="3" t="inlineStr"/>
-      <c r="AI2" s="3" t="inlineStr"/>
-      <c r="AJ2" s="3" t="inlineStr"/>
-      <c r="AK2" s="3" t="inlineStr"/>
-      <c r="AL2" s="3" t="inlineStr"/>
-      <c r="AM2" s="3" t="inlineStr"/>
-      <c r="AN2" s="3" t="inlineStr"/>
-      <c r="AO2" s="3" t="inlineStr">
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE52dFllc3N3TmFVX3VmQ3FUQ2xGTnlmcHFWQ25ZZHZEZ3ZuRm9Yd0dEamE0ekFlamE1VXFSYWJTZHNhNU1xbXRVTFBGaG5LZGpPM2FITk0tcDJsLTdBb2w2ZUtOOXRXODNyekk5Y0xHV1lMUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Denver Water</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr"/>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>NATURAL_DISASTER</t>
+        </is>
+      </c>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>drought</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>6e888bab541bf4b0c1f53b3a</t>
+        </is>
+      </c>
+      <c r="AD2" s="2" t="inlineStr">
+        <is>
+          <t>568cc21c4bc2a88c1be6ec1c</t>
+        </is>
+      </c>
+      <c r="AE2" s="2" t="inlineStr"/>
+      <c r="AF2" s="2" t="inlineStr"/>
+      <c r="AG2" s="2" t="inlineStr"/>
+      <c r="AH2" s="2" t="inlineStr"/>
+      <c r="AI2" s="2" t="inlineStr"/>
+      <c r="AJ2" s="2" t="inlineStr"/>
+      <c r="AK2" s="2" t="inlineStr"/>
+      <c r="AL2" s="2" t="inlineStr"/>
+      <c r="AM2" s="2" t="inlineStr"/>
+      <c r="AN2" s="2" t="inlineStr"/>
+      <c r="AO2" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AP2" s="3" t="inlineStr"/>
-      <c r="AQ2" s="3" t="inlineStr"/>
-      <c r="AR2" s="3" t="inlineStr"/>
-      <c r="AS2" s="3" t="inlineStr"/>
-      <c r="AT2" s="3" t="inlineStr"/>
-      <c r="AU2" s="3" t="inlineStr"/>
-      <c r="AV2" s="3" t="inlineStr"/>
-      <c r="AW2" s="3" t="inlineStr"/>
-      <c r="AX2" s="3" t="inlineStr"/>
-      <c r="AY2" s="3" t="inlineStr"/>
-      <c r="AZ2" s="3" t="inlineStr"/>
-      <c r="BA2" s="3" t="inlineStr"/>
-      <c r="BB2" s="3" t="inlineStr">
-        <is>
-          <t>AAPL</t>
-        </is>
-      </c>
-      <c r="BC2" s="3" t="inlineStr">
+      <c r="AP2" s="2" t="inlineStr"/>
+      <c r="AQ2" s="2" t="inlineStr"/>
+      <c r="AR2" s="2" t="inlineStr"/>
+      <c r="AS2" s="2" t="inlineStr"/>
+      <c r="AT2" s="2" t="inlineStr"/>
+      <c r="AU2" s="2" t="inlineStr"/>
+      <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" s="2" t="inlineStr"/>
+      <c r="AX2" s="2" t="inlineStr"/>
+      <c r="AY2" s="2" t="inlineStr"/>
+      <c r="AZ2" s="2" t="inlineStr"/>
+      <c r="BA2" s="2" t="inlineStr"/>
+      <c r="BB2" s="2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="BC2" s="2" t="inlineStr">
         <is>
           <t>主體證據不足</t>
         </is>
       </c>
-      <c r="BD2" s="3" t="inlineStr">
-        <is>
-          <t>AAPL</t>
-        </is>
-      </c>
-      <c r="BE2" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/nasdaqlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF2" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.654565+00:00</t>
-        </is>
-      </c>
-      <c r="BG2" s="3" t="inlineStr"/>
-      <c r="BH2" s="3" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>AT&amp;T</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-30T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Don’t forget the trees during drought!</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>天災</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>0.021</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr"/>
-      <c r="S3" s="2" t="inlineStr"/>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U3" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE52dFllc3N3TmFVX3VmQ3FUQ2xGTnlmcHFWQ25ZZHZEZ3ZuRm9Yd0dEamE0ekFlamE1VXFSYWJTZHNhNU1xbXRVTFBGaG5LZGpPM2FITk0tcDJsLTdBb2w2ZUtOOXRXODNyekk5Y0xHV1lMUQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Denver Water</t>
-        </is>
-      </c>
-      <c r="W3" s="2" t="inlineStr"/>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y3" s="2" t="inlineStr">
-        <is>
-          <t>NATURAL_DISASTER</t>
-        </is>
-      </c>
-      <c r="Z3" s="2" t="inlineStr">
-        <is>
-          <t>drought</t>
-        </is>
-      </c>
-      <c r="AA3" s="2" t="inlineStr"/>
-      <c r="AB3" s="2" t="inlineStr"/>
-      <c r="AC3" s="2" t="inlineStr">
-        <is>
-          <t>6e888bab541bf4b0c1f53b3a</t>
-        </is>
-      </c>
-      <c r="AD3" s="2" t="inlineStr">
-        <is>
-          <t>568cc21c4bc2a88c1be6ec1c</t>
-        </is>
-      </c>
-      <c r="AE3" s="2" t="inlineStr"/>
-      <c r="AF3" s="2" t="inlineStr"/>
-      <c r="AG3" s="2" t="inlineStr"/>
-      <c r="AH3" s="2" t="inlineStr"/>
-      <c r="AI3" s="2" t="inlineStr"/>
-      <c r="AJ3" s="2" t="inlineStr"/>
-      <c r="AK3" s="2" t="inlineStr"/>
-      <c r="AL3" s="2" t="inlineStr"/>
-      <c r="AM3" s="2" t="inlineStr"/>
-      <c r="AN3" s="2" t="inlineStr"/>
-      <c r="AO3" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP3" s="2" t="inlineStr"/>
-      <c r="AQ3" s="2" t="inlineStr"/>
-      <c r="AR3" s="2" t="inlineStr"/>
-      <c r="AS3" s="2" t="inlineStr"/>
-      <c r="AT3" s="2" t="inlineStr"/>
-      <c r="AU3" s="2" t="inlineStr"/>
-      <c r="AV3" s="2" t="inlineStr"/>
-      <c r="AW3" s="2" t="inlineStr"/>
-      <c r="AX3" s="2" t="inlineStr"/>
-      <c r="AY3" s="2" t="inlineStr"/>
-      <c r="AZ3" s="2" t="inlineStr"/>
-      <c r="BA3" s="2" t="inlineStr"/>
-      <c r="BB3" s="2" t="inlineStr">
+      <c r="BD2" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="BC3" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD3" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="BE3" s="2" t="inlineStr">
+      <c r="BE2" s="2" t="inlineStr">
         <is>
           <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
         </is>
       </c>
-      <c r="BF3" s="2" t="inlineStr">
+      <c r="BF2" s="2" t="inlineStr">
         <is>
           <t>2026-10-24T00:15:41.957209+00:00</t>
         </is>
       </c>
-      <c r="BG3" s="2" t="inlineStr"/>
-      <c r="BH3" s="2" t="inlineStr"/>
+      <c r="BG2" s="2" t="inlineStr"/>
+      <c r="BH2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr"/>
+      <c r="BL2" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH3"/>
+  <autoFilter ref="A1:BL2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4810,7 +4782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4873,6 +4845,10 @@
     <col width="22" customWidth="1" min="58" max="58"/>
     <col width="22" customWidth="1" min="59" max="59"/>
     <col width="22" customWidth="1" min="60" max="60"/>
+    <col width="22" customWidth="1" min="61" max="61"/>
+    <col width="22" customWidth="1" min="62" max="62"/>
+    <col width="22" customWidth="1" min="63" max="63"/>
+    <col width="22" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5176,9 +5152,29 @@
           <t>Ticker稽核警示</t>
         </is>
       </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>人工修改欄位</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>覆核註記</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核人</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>人工覆核時間</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BH1"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5189,7 +5185,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA5"/>
+  <dimension ref="A1:AA8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5239,134 +5235,134 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>methods</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>started_at</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>finished_at</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>llm_calls</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>cache_reused</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>major</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>selected_company_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>collected</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>rows</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>errors</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>stages</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>quota_reserved</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>重複合併</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>sources</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>rows</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>changed</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>missing_publication_time</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>ticker_statuses</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>llm_calls</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>start</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>end</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>methods</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>cache_reused</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>review</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>major</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>selected_company_count</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>collected</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>errors</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>stages</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>quota_reserved</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>重複合併</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ticker-audit-20261024-081549</t>
+          <t>daily-2026-10-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ticker-audit</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -5376,46 +5372,80 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296780+08:00</t>
+          <t>2026-10-25T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T08:15:49.296790+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>1691</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>257</v>
-      </c>
-      <c r="I2" s="2" t="n">
+          <t>2026-10-26T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:23:38.366332+08:00</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T08:40:53.776257+08:00</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="L2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr"/>
-      <c r="U2" s="2" t="inlineStr"/>
-      <c r="V2" s="2" t="inlineStr"/>
-      <c r="W2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="n">
+        <v>1926</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>503</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>1976</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 16 筆', '方法二 1958 筆；公司 503 家（非輪替）', '市場事件搜尋 2 筆', 'FinBERT 完成 1976 筆']</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>1961</v>
+      </c>
+      <c r="W2" s="2" t="n">
+        <v>15</v>
+      </c>
       <c r="X2" s="2" t="inlineStr"/>
       <c r="Y2" s="2" t="inlineStr"/>
       <c r="Z2" s="2" t="inlineStr"/>
@@ -5424,12 +5454,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+          <t>daily-2026-10-25</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -5439,90 +5469,94 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:26:34.299718+08:00</t>
+          <t>2026-10-24T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:32:11.776786+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
+          <t>2026-10-25T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:23:17.137147+08:00</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T08:40:12.120180+08:00</t>
+        </is>
+      </c>
       <c r="K3" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-22T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:26:32.508450+08:00</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>2032</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>503</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>34</v>
+        <v>2089</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="T3" s="2" t="n">
-        <v>17</v>
+        <v>2067</v>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 26 筆', '方法二 2059 筆；公司 503 家（非輪替）', '市場事件搜尋 6 筆', 'FinBERT 完成 2089 筆']</t>
+        </is>
       </c>
       <c r="U3" s="2" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X3" s="2" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
-      </c>
-      <c r="Y3" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="Z3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>2067</v>
+      </c>
+      <c r="W3" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="X3" s="2" t="inlineStr"/>
+      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr"/>
+      <c r="AA3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>daily-2026-10-24</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -5532,94 +5566,94 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:20:47.845317+08:00</t>
+          <t>2026-10-23T08:20:00+08:00</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:21:20.302846+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
+          <t>2026-10-24T08:20:00+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:44:09.884829+08:00</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T13:04:34.984103+08:00</t>
+        </is>
+      </c>
       <c r="K4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="b">
-        <v>1</v>
+        <v>35</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>3760</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>503</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>2</v>
+        <v>3802</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="T4" s="2" t="n">
-        <v>2</v>
+        <v>3825</v>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 158 筆', '方法二 3638 筆；公司 503 家（非輪替）', '市場事件搜尋 8 筆', 'FinBERT 完成 3802 筆']</t>
+        </is>
       </c>
       <c r="U4" s="2" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="V4" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X4" s="2" t="inlineStr">
-        <is>
-          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
-        </is>
-      </c>
-      <c r="Y4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA4" s="2" t="n">
-        <v>0</v>
-      </c>
+        <v>3793</v>
+      </c>
+      <c r="W4" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="X4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>ticker-audit-20261024-081549</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>manual</t>
+          <t>ticker-audit</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -5627,89 +5661,342 @@
           <t>success</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:11.949238+08:00</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:19:18.833437+08:00</t>
-        </is>
-      </c>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="n">
-        <v>33</v>
-      </c>
+      <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296780+08:00</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T08:15:49.296790+08:00</t>
+        </is>
+      </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:16:00+08:00</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="2" t="n">
-        <v>33</v>
-      </c>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
       <c r="R5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="T5" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="U5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="X5" s="2" t="inlineStr">
-        <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
-        </is>
+        <v>1691</v>
+      </c>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="n">
+        <v>19</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>1</v>
+        <v>257</v>
       </c>
       <c r="Z5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA5" s="2" t="n">
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
+          <t>{'已核對': 1429, '主體證據不足': 218, '人工確認': 20, '市場／多公司或主體待辨識': 10, '公司名稱／股票代號歧義': 7, '公司代號待核對': 4, '非本市場上市主體': 2, '非上市機構': 1}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:32.508450+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:26:34.299718+08:00</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:32:11.776786+08:00</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="M6" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="N6" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="2" t="inlineStr"/>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:20:47.845317+08:00</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:21:20.302846+08:00</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="R7" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="W7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="2" t="inlineStr"/>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:11.949238+08:00</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:18.833437+08:00</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="2" t="inlineStr"/>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA5"/>
+  <autoFilter ref="A1:AA8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/news_daily/2026-08-30.xlsx
+++ b/news_daily/2026-08-30.xlsx
@@ -15,8 +15,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$BL$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$BL$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$AA$8</definedName>
   </definedNames>
@@ -43,7 +43,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -58,11 +58,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFE0B2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF9C4"/>
       </patternFill>
     </fill>
   </fills>
@@ -84,7 +79,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -93,9 +88,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1810,32 +1802,32 @@
       <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>天災</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>待人工覆核</t>
+          <t>人工覆核</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1875,7 +1867,7 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>NATURAL_DISASTER</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
@@ -1884,7 +1876,11 @@
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr"/>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>079e04f39f3f46adb22486b763b2d27b</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
           <t>6e888bab541bf4b0c1f53b3a</t>
@@ -1907,7 +1903,7 @@
       <c r="AN7" s="2" t="inlineStr"/>
       <c r="AO7" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP7" s="2" t="inlineStr"/>
@@ -1949,10 +1945,22 @@
       </c>
       <c r="BG7" s="2" t="inlineStr"/>
       <c r="BH7" s="2" t="inlineStr"/>
-      <c r="BI7" s="2" t="inlineStr"/>
+      <c r="BI7" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ7" s="2" t="inlineStr"/>
-      <c r="BK7" s="2" t="inlineStr"/>
-      <c r="BL7" s="2" t="inlineStr"/>
+      <c r="BK7" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2691,170 +2699,194 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>COO</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Cooper Companies (The)</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>2026-08-30T00:37:26+08:00</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Nike Installs Former Foot Locker Supply Chain Chief as Converse COO</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr"/>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L12" s="4" t="inlineStr"/>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>原有新聞流程</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>0.039</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／別名核對</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQWDdCbklQanBQMkJ1YXBzR3hWNnlHM1B5ZU5aMDk3ZGpYR0o4X3IzN09WZDNNbmVLRUt1UHBBX1hxRTJoM2J3WE9EenZpT2pkeHZBekdwdlZmekhwaE9tMjlsRFI3WVFsTzdQbmZ2ZHg3QWhsZUYwWlhPRTQ1WEhSVzJHM1hvMlE4UVc1eEdVUElxSHh0SUozVw?oc=5</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>WWD</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr"/>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>OPERATIONS</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>supply chain</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>6605a6bd8423494abe4b7a7a866b691b</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>dc32a9237e8ca9638b26d5ec</t>
+        </is>
+      </c>
+      <c r="AD12" s="2" t="inlineStr">
+        <is>
+          <t>1f273c467c5ad0509a9b6b04</t>
+        </is>
+      </c>
+      <c r="AE12" s="2" t="inlineStr"/>
+      <c r="AF12" s="2" t="inlineStr"/>
+      <c r="AG12" s="2" t="inlineStr"/>
+      <c r="AH12" s="2" t="inlineStr"/>
+      <c r="AI12" s="2" t="inlineStr"/>
+      <c r="AJ12" s="2" t="inlineStr"/>
+      <c r="AK12" s="2" t="inlineStr"/>
+      <c r="AL12" s="2" t="inlineStr"/>
+      <c r="AM12" s="2" t="inlineStr"/>
+      <c r="AN12" s="2" t="inlineStr"/>
+      <c r="AO12" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O12" s="4" t="inlineStr">
-        <is>
-          <t>0.039</t>
-        </is>
-      </c>
-      <c r="P12" s="4" t="inlineStr"/>
-      <c r="Q12" s="4" t="inlineStr"/>
-      <c r="R12" s="4" t="inlineStr"/>
-      <c r="S12" s="4" t="inlineStr"/>
-      <c r="T12" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U12" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQWDdCbklQanBQMkJ1YXBzR3hWNnlHM1B5ZU5aMDk3ZGpYR0o4X3IzN09WZDNNbmVLRUt1UHBBX1hxRTJoM2J3WE9EenZpT2pkeHZBekdwdlZmekhwaE9tMjlsRFI3WVFsTzdQbmZ2ZHg3QWhsZUYwWlhPRTQ1WEhSVzJHM1hvMlE4UVc1eEdVUElxSHh0SUozVw?oc=5</t>
-        </is>
-      </c>
-      <c r="V12" s="4" t="inlineStr">
-        <is>
-          <t>WWD</t>
-        </is>
-      </c>
-      <c r="W12" s="4" t="inlineStr"/>
-      <c r="X12" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y12" s="4" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z12" s="4" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA12" s="4" t="inlineStr"/>
-      <c r="AB12" s="4" t="inlineStr"/>
-      <c r="AC12" s="4" t="inlineStr">
-        <is>
-          <t>dc32a9237e8ca9638b26d5ec</t>
-        </is>
-      </c>
-      <c r="AD12" s="4" t="inlineStr">
-        <is>
-          <t>1f273c467c5ad0509a9b6b04</t>
-        </is>
-      </c>
-      <c r="AE12" s="4" t="inlineStr"/>
-      <c r="AF12" s="4" t="inlineStr"/>
-      <c r="AG12" s="4" t="inlineStr"/>
-      <c r="AH12" s="4" t="inlineStr"/>
-      <c r="AI12" s="4" t="inlineStr"/>
-      <c r="AJ12" s="4" t="inlineStr"/>
-      <c r="AK12" s="4" t="inlineStr"/>
-      <c r="AL12" s="4" t="inlineStr"/>
-      <c r="AM12" s="4" t="inlineStr"/>
-      <c r="AN12" s="4" t="inlineStr"/>
-      <c r="AO12" s="4" t="inlineStr"/>
-      <c r="AP12" s="4" t="inlineStr"/>
-      <c r="AQ12" s="4" t="inlineStr"/>
-      <c r="AR12" s="4" t="inlineStr"/>
-      <c r="AS12" s="4" t="inlineStr"/>
-      <c r="AT12" s="4" t="inlineStr"/>
-      <c r="AU12" s="4" t="inlineStr"/>
-      <c r="AV12" s="4" t="inlineStr"/>
-      <c r="AW12" s="4" t="inlineStr"/>
-      <c r="AX12" s="4" t="inlineStr"/>
-      <c r="AY12" s="4" t="inlineStr"/>
-      <c r="AZ12" s="4" t="inlineStr"/>
-      <c r="BA12" s="4" t="inlineStr"/>
-      <c r="BB12" s="4" t="inlineStr">
+      <c r="AP12" s="2" t="inlineStr"/>
+      <c r="AQ12" s="2" t="inlineStr"/>
+      <c r="AR12" s="2" t="inlineStr"/>
+      <c r="AS12" s="2" t="inlineStr"/>
+      <c r="AT12" s="2" t="inlineStr"/>
+      <c r="AU12" s="2" t="inlineStr"/>
+      <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" s="2" t="inlineStr"/>
+      <c r="AX12" s="2" t="inlineStr"/>
+      <c r="AY12" s="2" t="inlineStr"/>
+      <c r="AZ12" s="2" t="inlineStr"/>
+      <c r="BA12" s="2" t="inlineStr"/>
+      <c r="BB12" s="2" t="inlineStr">
         <is>
           <t>COO</t>
         </is>
       </c>
-      <c r="BC12" s="4" t="inlineStr">
+      <c r="BC12" s="2" t="inlineStr">
         <is>
           <t>已核對</t>
         </is>
       </c>
-      <c r="BD12" s="4" t="inlineStr"/>
-      <c r="BE12" s="4" t="inlineStr">
+      <c r="BD12" s="2" t="inlineStr"/>
+      <c r="BE12" s="2" t="inlineStr">
         <is>
           <t>公司清單</t>
         </is>
       </c>
-      <c r="BF12" s="4" t="inlineStr"/>
-      <c r="BG12" s="4" t="inlineStr">
+      <c r="BF12" s="2" t="inlineStr"/>
+      <c r="BG12" s="2" t="inlineStr">
         <is>
           <t>公司清單／交易所參照</t>
         </is>
       </c>
-      <c r="BH12" s="4" t="inlineStr"/>
-      <c r="BI12" s="4" t="inlineStr"/>
-      <c r="BJ12" s="4" t="inlineStr"/>
-      <c r="BK12" s="4" t="inlineStr"/>
-      <c r="BL12" s="4" t="inlineStr"/>
+      <c r="BH12" s="2" t="inlineStr"/>
+      <c r="BI12" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
+      <c r="BJ12" s="2" t="inlineStr"/>
+      <c r="BK12" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T15:54:08.043808+08:00</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:BL12"/>
@@ -2868,7 +2900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL6"/>
+  <dimension ref="A1:BL5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4027,174 +4059,8 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>COO</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Cooper Companies (The)</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-30T00:37:26+08:00</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Nike Installs Former Foot Locker Supply Chain Chief as Converse COO</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>供應鏈中斷</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、加入觀察</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="inlineStr"/>
-      <c r="M6" s="4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N6" s="4" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O6" s="4" t="inlineStr">
-        <is>
-          <t>0.039</t>
-        </is>
-      </c>
-      <c r="P6" s="4" t="inlineStr"/>
-      <c r="Q6" s="4" t="inlineStr"/>
-      <c r="R6" s="4" t="inlineStr"/>
-      <c r="S6" s="4" t="inlineStr"/>
-      <c r="T6" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／別名核對</t>
-        </is>
-      </c>
-      <c r="U6" s="4" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQWDdCbklQanBQMkJ1YXBzR3hWNnlHM1B5ZU5aMDk3ZGpYR0o4X3IzN09WZDNNbmVLRUt1UHBBX1hxRTJoM2J3WE9EenZpT2pkeHZBekdwdlZmekhwaE9tMjlsRFI3WVFsTzdQbmZ2ZHg3QWhsZUYwWlhPRTQ1WEhSVzJHM1hvMlE4UVc1eEdVUElxSHh0SUozVw?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="4" t="inlineStr">
-        <is>
-          <t>WWD</t>
-        </is>
-      </c>
-      <c r="W6" s="4" t="inlineStr"/>
-      <c r="X6" s="4" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y6" s="4" t="inlineStr">
-        <is>
-          <t>SUPPLY_CHAIN_DISRUPTION</t>
-        </is>
-      </c>
-      <c r="Z6" s="4" t="inlineStr">
-        <is>
-          <t>supply chain</t>
-        </is>
-      </c>
-      <c r="AA6" s="4" t="inlineStr"/>
-      <c r="AB6" s="4" t="inlineStr"/>
-      <c r="AC6" s="4" t="inlineStr">
-        <is>
-          <t>dc32a9237e8ca9638b26d5ec</t>
-        </is>
-      </c>
-      <c r="AD6" s="4" t="inlineStr">
-        <is>
-          <t>1f273c467c5ad0509a9b6b04</t>
-        </is>
-      </c>
-      <c r="AE6" s="4" t="inlineStr"/>
-      <c r="AF6" s="4" t="inlineStr"/>
-      <c r="AG6" s="4" t="inlineStr"/>
-      <c r="AH6" s="4" t="inlineStr"/>
-      <c r="AI6" s="4" t="inlineStr"/>
-      <c r="AJ6" s="4" t="inlineStr"/>
-      <c r="AK6" s="4" t="inlineStr"/>
-      <c r="AL6" s="4" t="inlineStr"/>
-      <c r="AM6" s="4" t="inlineStr"/>
-      <c r="AN6" s="4" t="inlineStr"/>
-      <c r="AO6" s="4" t="inlineStr"/>
-      <c r="AP6" s="4" t="inlineStr"/>
-      <c r="AQ6" s="4" t="inlineStr"/>
-      <c r="AR6" s="4" t="inlineStr"/>
-      <c r="AS6" s="4" t="inlineStr"/>
-      <c r="AT6" s="4" t="inlineStr"/>
-      <c r="AU6" s="4" t="inlineStr"/>
-      <c r="AV6" s="4" t="inlineStr"/>
-      <c r="AW6" s="4" t="inlineStr"/>
-      <c r="AX6" s="4" t="inlineStr"/>
-      <c r="AY6" s="4" t="inlineStr"/>
-      <c r="AZ6" s="4" t="inlineStr"/>
-      <c r="BA6" s="4" t="inlineStr"/>
-      <c r="BB6" s="4" t="inlineStr">
-        <is>
-          <t>COO</t>
-        </is>
-      </c>
-      <c r="BC6" s="4" t="inlineStr">
-        <is>
-          <t>已核對</t>
-        </is>
-      </c>
-      <c r="BD6" s="4" t="inlineStr"/>
-      <c r="BE6" s="4" t="inlineStr">
-        <is>
-          <t>公司清單</t>
-        </is>
-      </c>
-      <c r="BF6" s="4" t="inlineStr"/>
-      <c r="BG6" s="4" t="inlineStr">
-        <is>
-          <t>公司清單／交易所參照</t>
-        </is>
-      </c>
-      <c r="BH6" s="4" t="inlineStr"/>
-      <c r="BI6" s="4" t="inlineStr"/>
-      <c r="BJ6" s="4" t="inlineStr"/>
-      <c r="BK6" s="4" t="inlineStr"/>
-      <c r="BL6" s="4" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:BL6"/>
+  <autoFilter ref="A1:BL5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4205,7 +4071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL2"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4596,182 +4462,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>AT&amp;T</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-30T15:00:00+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Don’t forget the trees during drought!</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>天災</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>僅紀錄</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>原有新聞流程</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>0.021</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE52dFllc3N3TmFVX3VmQ3FUQ2xGTnlmcHFWQ25ZZHZEZ3ZuRm9Yd0dEamE0ekFlamE1VXFSYWJTZHNhNU1xbXRVTFBGaG5LZGpPM2FITk0tcDJsLTdBb2w2ZUtOOXRXODNyekk5Y0xHV1lMUQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>Denver Water</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr"/>
-      <c r="X2" s="2" t="inlineStr">
-        <is>
-          <t>OPERATIONS</t>
-        </is>
-      </c>
-      <c r="Y2" s="2" t="inlineStr">
-        <is>
-          <t>NATURAL_DISASTER</t>
-        </is>
-      </c>
-      <c r="Z2" s="2" t="inlineStr">
-        <is>
-          <t>drought</t>
-        </is>
-      </c>
-      <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
-      <c r="AC2" s="2" t="inlineStr">
-        <is>
-          <t>6e888bab541bf4b0c1f53b3a</t>
-        </is>
-      </c>
-      <c r="AD2" s="2" t="inlineStr">
-        <is>
-          <t>568cc21c4bc2a88c1be6ec1c</t>
-        </is>
-      </c>
-      <c r="AE2" s="2" t="inlineStr"/>
-      <c r="AF2" s="2" t="inlineStr"/>
-      <c r="AG2" s="2" t="inlineStr"/>
-      <c r="AH2" s="2" t="inlineStr"/>
-      <c r="AI2" s="2" t="inlineStr"/>
-      <c r="AJ2" s="2" t="inlineStr"/>
-      <c r="AK2" s="2" t="inlineStr"/>
-      <c r="AL2" s="2" t="inlineStr"/>
-      <c r="AM2" s="2" t="inlineStr"/>
-      <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AP2" s="2" t="inlineStr"/>
-      <c r="AQ2" s="2" t="inlineStr"/>
-      <c r="AR2" s="2" t="inlineStr"/>
-      <c r="AS2" s="2" t="inlineStr"/>
-      <c r="AT2" s="2" t="inlineStr"/>
-      <c r="AU2" s="2" t="inlineStr"/>
-      <c r="AV2" s="2" t="inlineStr"/>
-      <c r="AW2" s="2" t="inlineStr"/>
-      <c r="AX2" s="2" t="inlineStr"/>
-      <c r="AY2" s="2" t="inlineStr"/>
-      <c r="AZ2" s="2" t="inlineStr"/>
-      <c r="BA2" s="2" t="inlineStr"/>
-      <c r="BB2" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="BC2" s="2" t="inlineStr">
-        <is>
-          <t>主體證據不足</t>
-        </is>
-      </c>
-      <c r="BD2" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="BE2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.nasdaqtrader.com/dynamic/SymDir/otherlisted.txt</t>
-        </is>
-      </c>
-      <c r="BF2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-24T00:15:41.957209+00:00</t>
-        </is>
-      </c>
-      <c r="BG2" s="2" t="inlineStr"/>
-      <c r="BH2" s="2" t="inlineStr"/>
-      <c r="BI2" s="2" t="inlineStr"/>
-      <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:BL2"/>
+  <autoFilter ref="A1:BL1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/news_daily/2026-08-30.xlsx
+++ b/news_daily/2026-08-30.xlsx
@@ -880,28 +880,32 @@
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -941,7 +945,7 @@
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -950,7 +954,11 @@
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>cfa9ff81e6aa423ba78e1e31cff1b61f</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>03afdd2d1915c2d18473be60</t>
@@ -971,7 +979,11 @@
       <c r="AL2" s="2" t="inlineStr"/>
       <c r="AM2" s="2" t="inlineStr"/>
       <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP2" s="2" t="inlineStr"/>
       <c r="AQ2" s="2" t="inlineStr"/>
       <c r="AR2" s="2" t="inlineStr"/>
@@ -1015,10 +1027,22 @@
         </is>
       </c>
       <c r="BH2" s="2" t="inlineStr"/>
-      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BI2" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ2" s="2" t="inlineStr"/>
-      <c r="BK2" s="2" t="inlineStr"/>
-      <c r="BL2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1240,28 +1264,32 @@
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>分析師降評</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -1301,7 +1329,7 @@
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>ANALYST_DOWNGRADE</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -1310,7 +1338,11 @@
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr"/>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>9399f4c32b0c41c98f0dae0112979a4a</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
           <t>f0cd89d0866fc75a3512c647</t>
@@ -1331,7 +1363,11 @@
       <c r="AL4" s="2" t="inlineStr"/>
       <c r="AM4" s="2" t="inlineStr"/>
       <c r="AN4" s="2" t="inlineStr"/>
-      <c r="AO4" s="2" t="inlineStr"/>
+      <c r="AO4" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP4" s="2" t="inlineStr"/>
       <c r="AQ4" s="2" t="inlineStr"/>
       <c r="AR4" s="2" t="inlineStr"/>
@@ -1375,10 +1411,22 @@
         </is>
       </c>
       <c r="BH4" s="2" t="inlineStr"/>
-      <c r="BI4" s="2" t="inlineStr"/>
+      <c r="BI4" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ4" s="2" t="inlineStr"/>
-      <c r="BK4" s="2" t="inlineStr"/>
-      <c r="BL4" s="2" t="inlineStr"/>
+      <c r="BK4" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -2011,13 +2059,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2066,7 +2118,11 @@
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr"/>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>355e7d8784264a51a52dc31045658313</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
           <t>9f6744e482e5983fa1612f8d</t>
@@ -2087,7 +2143,11 @@
       <c r="AL8" s="2" t="inlineStr"/>
       <c r="AM8" s="2" t="inlineStr"/>
       <c r="AN8" s="2" t="inlineStr"/>
-      <c r="AO8" s="2" t="inlineStr"/>
+      <c r="AO8" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP8" s="2" t="inlineStr"/>
       <c r="AQ8" s="2" t="inlineStr"/>
       <c r="AR8" s="2" t="inlineStr"/>
@@ -2133,8 +2193,16 @@
       <c r="BH8" s="2" t="inlineStr"/>
       <c r="BI8" s="2" t="inlineStr"/>
       <c r="BJ8" s="2" t="inlineStr"/>
-      <c r="BK8" s="2" t="inlineStr"/>
-      <c r="BL8" s="2" t="inlineStr"/>
+      <c r="BK8" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2170,28 +2238,32 @@
       <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>估值疑慮</t>
+          <t>無關新聞事件</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>僅紀錄</t>
+          <t>排除、不納入風險事件</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>規則</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
+          <t>人工覆核</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>人工覆核</t>
+        </is>
+      </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2231,7 +2303,7 @@
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>VALUATION_CONCERN</t>
+          <t>NOT_RELEVANT</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
@@ -2240,7 +2312,11 @@
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr"/>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>6c112ca06749437b98f7a5dd888adbc3</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
           <t>cd6eaa0d3ae3ed599d4ac475</t>
@@ -2261,7 +2337,11 @@
       <c r="AL9" s="2" t="inlineStr"/>
       <c r="AM9" s="2" t="inlineStr"/>
       <c r="AN9" s="2" t="inlineStr"/>
-      <c r="AO9" s="2" t="inlineStr"/>
+      <c r="AO9" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AP9" s="2" t="inlineStr"/>
       <c r="AQ9" s="2" t="inlineStr"/>
       <c r="AR9" s="2" t="inlineStr"/>
@@ -2305,10 +2385,22 @@
         </is>
       </c>
       <c r="BH9" s="2" t="inlineStr"/>
-      <c r="BI9" s="2" t="inlineStr"/>
+      <c r="BI9" s="2" t="inlineStr">
+        <is>
+          <t>Action|Event_Code|Level|事件中文</t>
+        </is>
+      </c>
       <c r="BJ9" s="2" t="inlineStr"/>
-      <c r="BK9" s="2" t="inlineStr"/>
-      <c r="BL9" s="2" t="inlineStr"/>
+      <c r="BK9" s="2" t="inlineStr">
+        <is>
+          <t>離線覆核</t>
+        </is>
+      </c>
+      <c r="BL9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-26T16:20:22.024687+08:00</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">

--- a/news_daily/2026-08-30.xlsx
+++ b/news_daily/2026-08-30.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整新聞" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="主要負面事件" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待人工覆核" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待補分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$BL$12</definedName>
@@ -27,16 +27,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -61,7 +58,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -69,21 +66,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1055,7 +1044,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr"/>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Apple Inc.</t>
@@ -1215,7 +1208,7 @@
       <c r="BH3" s="3" t="inlineStr"/>
       <c r="BI3" s="3" t="inlineStr">
         <is>
-          <t>Event_Code|Level|事件中文</t>
+          <t>Event_Code|Level|Ticker|事件中文</t>
         </is>
       </c>
       <c r="BJ3" s="3" t="inlineStr"/>
@@ -3394,7 +3387,11 @@
           <t>US</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Apple Inc.</t>
@@ -3554,7 +3551,7 @@
       <c r="BH2" s="3" t="inlineStr"/>
       <c r="BI2" s="3" t="inlineStr">
         <is>
-          <t>Event_Code|Level|事件中文</t>
+          <t>Event_Code|Level|Ticker|事件中文</t>
         </is>
       </c>
       <c r="BJ2" s="3" t="inlineStr"/>
